--- a/tests/conversions_check.xlsx
+++ b/tests/conversions_check.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\unyts\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508DAC16-EDB9-439D-A3C6-ECD5C66B8E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E99D13-D002-46AC-BEE2-DEA0C6B4C2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="2844" windowWidth="21708" windowHeight="20328" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="49176" yWindow="2160" windowWidth="36156" windowHeight="19512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2256</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4526" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4532" uniqueCount="1164">
   <si>
     <t>source</t>
   </si>
@@ -3520,6 +3520,12 @@
   </si>
   <si>
     <t>qm3</t>
+  </si>
+  <si>
+    <t>skip</t>
+  </si>
+  <si>
+    <t>sip</t>
   </si>
 </sst>
 </file>
@@ -3879,7 +3885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2261"/>
+  <dimension ref="A1:G2262"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -3887,7 +3893,7 @@
     <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>1005</v>
       </c>
@@ -3906,8 +3912,11 @@
       <c r="F1" s="2" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -3928,7 +3937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3949,7 +3958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3970,7 +3979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3991,7 +4000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4012,7 +4021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4033,7 +4042,7 @@
         <v>1.0000000000000001E-9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4054,7 +4063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4075,7 +4084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4096,7 +4105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4117,7 +4126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4138,7 +4147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4159,7 +4168,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4180,7 +4189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4201,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -16318,7 +16327,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>591</v>
       </c>
@@ -16339,7 +16348,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>592</v>
       </c>
@@ -16360,7 +16369,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>593</v>
       </c>
@@ -16381,7 +16390,7 @@
         <v>1E+18</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>594</v>
       </c>
@@ -16402,7 +16411,7 @@
         <v>1E+18</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>595</v>
       </c>
@@ -16423,7 +16432,7 @@
         <v>1E+27</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>596</v>
       </c>
@@ -16444,7 +16453,7 @@
         <v>1E+36</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>597</v>
       </c>
@@ -16465,7 +16474,7 @@
         <v>9.9999999999999993E+44</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>598</v>
       </c>
@@ -16486,7 +16495,7 @@
         <v>1.0000000000000001E+54</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>599</v>
       </c>
@@ -16507,7 +16516,7 @@
         <v>1.0000000000000001E+63</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>600</v>
       </c>
@@ -16528,7 +16537,7 @@
         <v>9.9999999999999994E+71</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>601</v>
       </c>
@@ -16548,8 +16557,11 @@
       <c r="F603">
         <v>9.9999999999999992E+80</v>
       </c>
-    </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G603" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>602</v>
       </c>
@@ -16570,7 +16582,7 @@
         <v>9.9999999999999997E+89</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>603</v>
       </c>
@@ -16591,7 +16603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>604</v>
       </c>
@@ -16612,7 +16624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>605</v>
       </c>
@@ -16633,7 +16645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>606</v>
       </c>
@@ -40700,7 +40712,7 @@
         <v>1752</v>
       </c>
       <c r="B1754" s="2" t="str">
-        <f t="shared" ref="B1754:B1817" si="28">C1754&amp;" -&gt; " &amp;D1754</f>
+        <f t="shared" ref="B1754:B1818" si="28">C1754&amp;" -&gt; " &amp;D1754</f>
         <v>lb/stb -&gt; LB/STB</v>
       </c>
       <c r="C1754" t="s">
@@ -41163,13 +41175,13 @@
       </c>
       <c r="B1776" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psi -&gt; µsip</v>
+        <v>1/psi -&gt; sip</v>
       </c>
       <c r="C1776" t="s">
         <v>858</v>
       </c>
       <c r="D1776" t="s">
-        <v>860</v>
+        <v>1163</v>
       </c>
       <c r="E1776">
         <v>1</v>
@@ -41178,61 +41190,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1777" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1777" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1777" s="1">
         <v>1775</v>
       </c>
       <c r="B1777" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psi -&gt; usip</v>
+        <v>1/psi -&gt; µsip</v>
       </c>
       <c r="C1777" t="s">
         <v>858</v>
       </c>
       <c r="D1777" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E1777">
         <v>1</v>
       </c>
-      <c r="F1777">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1778" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1777" s="4">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1778" s="1">
         <v>1776</v>
       </c>
       <c r="B1778" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psi -&gt; 1/psig</v>
+        <v>1/psi -&gt; usip</v>
       </c>
       <c r="C1778" t="s">
         <v>858</v>
       </c>
       <c r="D1778" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E1778">
         <v>1</v>
       </c>
-      <c r="F1778">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1779" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1778" s="4">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1779" s="1">
         <v>1777</v>
       </c>
       <c r="B1779" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psi -&gt; 1/PSI</v>
+        <v>1/psi -&gt; 1/psig</v>
       </c>
       <c r="C1779" t="s">
         <v>858</v>
       </c>
       <c r="D1779" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E1779">
         <v>1</v>
@@ -41241,19 +41253,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1780" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1780" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1780" s="1">
         <v>1778</v>
       </c>
       <c r="B1780" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psia -&gt; 1/psi</v>
+        <v>1/psi -&gt; 1/PSI</v>
       </c>
       <c r="C1780" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D1780" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="E1780">
         <v>1</v>
@@ -41262,19 +41274,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1781" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1781" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1781" s="1">
         <v>1779</v>
       </c>
       <c r="B1781" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psia -&gt; 1/PSIA</v>
+        <v>1/psia -&gt; 1/psi</v>
       </c>
       <c r="C1781" t="s">
         <v>859</v>
       </c>
       <c r="D1781" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="E1781">
         <v>1</v>
@@ -41283,19 +41295,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1782" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1782" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1782" s="1">
         <v>1780</v>
       </c>
       <c r="B1782" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>µsip -&gt; 1/psi</v>
+        <v>1/psia -&gt; 1/PSIA</v>
       </c>
       <c r="C1782" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D1782" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="E1782">
         <v>1</v>
@@ -41304,40 +41316,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1783" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1783" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1783" s="1">
         <v>1781</v>
       </c>
       <c r="B1783" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>µsip -&gt; usip</v>
+        <v>µsip -&gt; 1/psi</v>
       </c>
       <c r="C1783" t="s">
         <v>860</v>
       </c>
       <c r="D1783" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="E1783">
         <v>1</v>
       </c>
-      <c r="F1783">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1784" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1783" s="4">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1784" s="1">
         <v>1782</v>
       </c>
       <c r="B1784" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>µsip -&gt; ΜSIP</v>
+        <v>µsip -&gt; usip</v>
       </c>
       <c r="C1784" t="s">
         <v>860</v>
       </c>
       <c r="D1784" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="E1784">
         <v>1</v>
@@ -41346,19 +41358,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1785" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1785" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1785" s="1">
         <v>1783</v>
       </c>
       <c r="B1785" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>usip -&gt; 1/psi</v>
+        <v>µsip -&gt; ΜSIP</v>
       </c>
       <c r="C1785" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D1785" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="E1785">
         <v>1</v>
@@ -41366,41 +41378,44 @@
       <c r="F1785">
         <v>1</v>
       </c>
-    </row>
-    <row r="1786" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1785" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1786" s="1">
         <v>1784</v>
       </c>
       <c r="B1786" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>usip -&gt; µsip</v>
+        <v>usip -&gt; 1/psi</v>
       </c>
       <c r="C1786" t="s">
         <v>861</v>
       </c>
       <c r="D1786" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E1786">
         <v>1</v>
       </c>
-      <c r="F1786">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1787" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1786" s="4">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1787" s="1">
         <v>1785</v>
       </c>
       <c r="B1787" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>usip -&gt; USIP</v>
+        <v>usip -&gt; µsip</v>
       </c>
       <c r="C1787" t="s">
         <v>861</v>
       </c>
       <c r="D1787" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="E1787">
         <v>1</v>
@@ -41409,19 +41424,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1788" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1788" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1788" s="1">
         <v>1786</v>
       </c>
       <c r="B1788" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psig -&gt; 1/psi</v>
+        <v>usip -&gt; USIP</v>
       </c>
       <c r="C1788" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D1788" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="E1788">
         <v>1</v>
@@ -41430,19 +41445,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1789" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1789" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1789" s="1">
         <v>1787</v>
       </c>
       <c r="B1789" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/psig -&gt; 1/PSIG</v>
+        <v>1/psig -&gt; 1/psi</v>
       </c>
       <c r="C1789" t="s">
         <v>862</v>
       </c>
       <c r="D1789" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="E1789">
         <v>1</v>
@@ -41451,19 +41466,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1790" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1790" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1790" s="1">
         <v>1788</v>
       </c>
       <c r="B1790" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/bar -&gt; 1/bara</v>
+        <v>1/psig -&gt; 1/PSIG</v>
       </c>
       <c r="C1790" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D1790" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="E1790">
         <v>1</v>
@@ -41472,19 +41487,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1791" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1791" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1791" s="1">
         <v>1789</v>
       </c>
       <c r="B1791" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/bar -&gt; 1/barg</v>
+        <v>1/bar -&gt; 1/bara</v>
       </c>
       <c r="C1791" t="s">
         <v>863</v>
       </c>
       <c r="D1791" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E1791">
         <v>1</v>
@@ -41493,19 +41508,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1792" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1792" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1792" s="1">
         <v>1790</v>
       </c>
       <c r="B1792" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/bar -&gt; 1/BAR</v>
+        <v>1/bar -&gt; 1/barg</v>
       </c>
       <c r="C1792" t="s">
         <v>863</v>
       </c>
       <c r="D1792" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="E1792">
         <v>1</v>
@@ -41514,19 +41529,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1793" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1793" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1793" s="1">
         <v>1791</v>
       </c>
       <c r="B1793" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/bara -&gt; 1/bar</v>
+        <v>1/bar -&gt; 1/BAR</v>
       </c>
       <c r="C1793" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D1793" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="E1793">
         <v>1</v>
@@ -41535,19 +41550,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1794" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1794" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1794" s="1">
         <v>1792</v>
       </c>
       <c r="B1794" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/bara -&gt; 1/BARA</v>
+        <v>1/bara -&gt; 1/bar</v>
       </c>
       <c r="C1794" t="s">
         <v>864</v>
       </c>
       <c r="D1794" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="E1794">
         <v>1</v>
@@ -41556,19 +41571,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1795" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1795" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1795" s="1">
         <v>1793</v>
       </c>
       <c r="B1795" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/barg -&gt; 1/bar</v>
+        <v>1/bara -&gt; 1/BARA</v>
       </c>
       <c r="C1795" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D1795" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="E1795">
         <v>1</v>
@@ -41577,19 +41592,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1796" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1796" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1796" s="1">
         <v>1794</v>
       </c>
       <c r="B1796" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/barg -&gt; 1/BARG</v>
+        <v>1/barg -&gt; 1/bar</v>
       </c>
       <c r="C1796" t="s">
         <v>865</v>
       </c>
       <c r="D1796" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="E1796">
         <v>1</v>
@@ -41598,19 +41613,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1797" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1797" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1797" s="1">
         <v>1795</v>
       </c>
       <c r="B1797" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/PSI -&gt; 1/psi</v>
+        <v>1/barg -&gt; 1/BARG</v>
       </c>
       <c r="C1797" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D1797" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="E1797">
         <v>1</v>
@@ -41619,19 +41634,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1798" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1798" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1798" s="1">
         <v>1796</v>
       </c>
       <c r="B1798" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/PSIA -&gt; 1/psia</v>
+        <v>1/PSI -&gt; 1/psi</v>
       </c>
       <c r="C1798" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D1798" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E1798">
         <v>1</v>
@@ -41640,19 +41655,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1799" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1799" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1799" s="1">
         <v>1797</v>
       </c>
       <c r="B1799" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>ΜSIP -&gt; µsip</v>
+        <v>1/PSIA -&gt; 1/psia</v>
       </c>
       <c r="C1799" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D1799" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E1799">
         <v>1</v>
@@ -41661,19 +41676,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1800" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1800" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1800" s="1">
         <v>1798</v>
       </c>
       <c r="B1800" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>USIP -&gt; usip</v>
+        <v>ΜSIP -&gt; µsip</v>
       </c>
       <c r="C1800" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D1800" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E1800">
         <v>1</v>
@@ -41681,20 +41696,23 @@
       <c r="F1800">
         <v>1</v>
       </c>
-    </row>
-    <row r="1801" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1800" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1801" s="1">
         <v>1799</v>
       </c>
       <c r="B1801" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/PSIG -&gt; 1/psig</v>
+        <v>USIP -&gt; usip</v>
       </c>
       <c r="C1801" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D1801" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E1801">
         <v>1</v>
@@ -41703,19 +41721,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1802" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1802" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1802" s="1">
         <v>1800</v>
       </c>
       <c r="B1802" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/BAR -&gt; 1/bar</v>
+        <v>1/PSIG -&gt; 1/psig</v>
       </c>
       <c r="C1802" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D1802" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E1802">
         <v>1</v>
@@ -41724,19 +41742,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1803" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1803" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1803" s="1">
         <v>1801</v>
       </c>
       <c r="B1803" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/BARA -&gt; 1/bara</v>
+        <v>1/BAR -&gt; 1/bar</v>
       </c>
       <c r="C1803" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D1803" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E1803">
         <v>1</v>
@@ -41745,19 +41763,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1804" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1804" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1804" s="1">
         <v>1802</v>
       </c>
       <c r="B1804" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>1/BARG -&gt; 1/barg</v>
+        <v>1/BARA -&gt; 1/bara</v>
       </c>
       <c r="C1804" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D1804" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E1804">
         <v>1</v>
@@ -41766,19 +41784,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1805" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1805" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1805" s="1">
         <v>1803</v>
       </c>
       <c r="B1805" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>stb/day -&gt; stbd</v>
+        <v>1/BARG -&gt; 1/barg</v>
       </c>
       <c r="C1805" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D1805" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="E1805">
         <v>1</v>
@@ -41787,19 +41805,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1806" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1806" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1806" s="1">
         <v>1804</v>
       </c>
       <c r="B1806" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>stb/day -&gt; STB/DAY</v>
+        <v>stb/day -&gt; stbd</v>
       </c>
       <c r="C1806" t="s">
         <v>874</v>
       </c>
       <c r="D1806" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="E1806">
         <v>1</v>
@@ -41808,19 +41826,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1807" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1807" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1807" s="1">
         <v>1805</v>
       </c>
       <c r="B1807" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>stbd -&gt; stb/day</v>
+        <v>stb/day -&gt; STB/DAY</v>
       </c>
       <c r="C1807" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D1807" t="s">
-        <v>874</v>
+        <v>888</v>
       </c>
       <c r="E1807">
         <v>1</v>
@@ -41829,19 +41847,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1808" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1808" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1808" s="1">
         <v>1806</v>
       </c>
       <c r="B1808" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>stbd -&gt; STBD</v>
+        <v>stbd -&gt; stb/day</v>
       </c>
       <c r="C1808" t="s">
         <v>875</v>
       </c>
       <c r="D1808" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="E1808">
         <v>1</v>
@@ -41856,13 +41874,13 @@
       </c>
       <c r="B1809" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>scf/day -&gt; scfd</v>
+        <v>stbd -&gt; STBD</v>
       </c>
       <c r="C1809" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D1809" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="E1809">
         <v>1</v>
@@ -41877,13 +41895,13 @@
       </c>
       <c r="B1810" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>scf/day -&gt; cf/day</v>
+        <v>scf/day -&gt; scfd</v>
       </c>
       <c r="C1810" t="s">
         <v>876</v>
       </c>
       <c r="D1810" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E1810">
         <v>1</v>
@@ -41898,13 +41916,13 @@
       </c>
       <c r="B1811" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>scf/day -&gt; SCF/DAY</v>
+        <v>scf/day -&gt; cf/day</v>
       </c>
       <c r="C1811" t="s">
         <v>876</v>
       </c>
       <c r="D1811" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="E1811">
         <v>1</v>
@@ -41919,13 +41937,13 @@
       </c>
       <c r="B1812" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>scfd -&gt; scf/day</v>
+        <v>scf/day -&gt; SCF/DAY</v>
       </c>
       <c r="C1812" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D1812" t="s">
-        <v>876</v>
+        <v>890</v>
       </c>
       <c r="E1812">
         <v>1</v>
@@ -41940,13 +41958,13 @@
       </c>
       <c r="B1813" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>scfd -&gt; SCFD</v>
+        <v>scfd -&gt; scf/day</v>
       </c>
       <c r="C1813" t="s">
         <v>877</v>
       </c>
       <c r="D1813" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="E1813">
         <v>1</v>
@@ -41961,13 +41979,13 @@
       </c>
       <c r="B1814" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>cf/day -&gt; scf/day</v>
+        <v>scfd -&gt; SCFD</v>
       </c>
       <c r="C1814" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D1814" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="E1814">
         <v>1</v>
@@ -41982,13 +42000,13 @@
       </c>
       <c r="B1815" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>cf/day -&gt; ft3/day</v>
+        <v>cf/day -&gt; scf/day</v>
       </c>
       <c r="C1815" t="s">
         <v>878</v>
       </c>
       <c r="D1815" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="E1815">
         <v>1</v>
@@ -42003,13 +42021,13 @@
       </c>
       <c r="B1816" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>cf/day -&gt; CF/DAY</v>
+        <v>cf/day -&gt; ft3/day</v>
       </c>
       <c r="C1816" t="s">
         <v>878</v>
       </c>
       <c r="D1816" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="E1816">
         <v>1</v>
@@ -42024,13 +42042,13 @@
       </c>
       <c r="B1817" s="2" t="str">
         <f t="shared" si="28"/>
-        <v>sm3/day -&gt; sm3d</v>
+        <v>cf/day -&gt; CF/DAY</v>
       </c>
       <c r="C1817" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D1817" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="E1817">
         <v>1</v>
@@ -42044,14 +42062,14 @@
         <v>1816</v>
       </c>
       <c r="B1818" s="2" t="str">
-        <f t="shared" ref="B1818:B1888" si="29">C1818&amp;" -&gt; " &amp;D1818</f>
-        <v>sm3/day -&gt; stm3d</v>
+        <f t="shared" si="28"/>
+        <v>sm3/day -&gt; sm3d</v>
       </c>
       <c r="C1818" t="s">
         <v>879</v>
       </c>
       <c r="D1818" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E1818">
         <v>1</v>
@@ -42065,14 +42083,14 @@
         <v>1817</v>
       </c>
       <c r="B1819" s="2" t="str">
-        <f t="shared" si="29"/>
-        <v>sm3/day -&gt; stm3/day</v>
+        <f t="shared" ref="B1819:B1889" si="29">C1819&amp;" -&gt; " &amp;D1819</f>
+        <v>sm3/day -&gt; stm3d</v>
       </c>
       <c r="C1819" t="s">
         <v>879</v>
       </c>
       <c r="D1819" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E1819">
         <v>1</v>
@@ -42087,13 +42105,13 @@
       </c>
       <c r="B1820" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>sm3/day -&gt; SM3/DAY</v>
+        <v>sm3/day -&gt; stm3/day</v>
       </c>
       <c r="C1820" t="s">
         <v>879</v>
       </c>
       <c r="D1820" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="E1820">
         <v>1</v>
@@ -42108,13 +42126,13 @@
       </c>
       <c r="B1821" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>sm3d -&gt; sm3/day</v>
+        <v>sm3/day -&gt; SM3/DAY</v>
       </c>
       <c r="C1821" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D1821" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="E1821">
         <v>1</v>
@@ -42129,13 +42147,13 @@
       </c>
       <c r="B1822" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>sm3d -&gt; SM3D</v>
+        <v>sm3d -&gt; sm3/day</v>
       </c>
       <c r="C1822" t="s">
         <v>880</v>
       </c>
       <c r="D1822" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="E1822">
         <v>1</v>
@@ -42150,13 +42168,13 @@
       </c>
       <c r="B1823" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>stm3d -&gt; sm3/day</v>
+        <v>sm3d -&gt; SM3D</v>
       </c>
       <c r="C1823" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D1823" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="E1823">
         <v>1</v>
@@ -42171,13 +42189,13 @@
       </c>
       <c r="B1824" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>stm3d -&gt; STM3D</v>
+        <v>stm3d -&gt; sm3/day</v>
       </c>
       <c r="C1824" t="s">
         <v>881</v>
       </c>
       <c r="D1824" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="E1824">
         <v>1</v>
@@ -42192,13 +42210,13 @@
       </c>
       <c r="B1825" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>stm3/day -&gt; sm3/day</v>
+        <v>stm3d -&gt; STM3D</v>
       </c>
       <c r="C1825" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D1825" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="E1825">
         <v>1</v>
@@ -42213,13 +42231,13 @@
       </c>
       <c r="B1826" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>stm3/day -&gt; STM3/DAY</v>
+        <v>stm3/day -&gt; sm3/day</v>
       </c>
       <c r="C1826" t="s">
         <v>882</v>
       </c>
       <c r="D1826" t="s">
-        <v>896</v>
+        <v>879</v>
       </c>
       <c r="E1826">
         <v>1</v>
@@ -42234,13 +42252,13 @@
       </c>
       <c r="B1827" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bbl/day -&gt; bbld</v>
+        <v>stm3/day -&gt; STM3/DAY</v>
       </c>
       <c r="C1827" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D1827" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="E1827">
         <v>1</v>
@@ -42255,13 +42273,13 @@
       </c>
       <c r="B1828" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bbl/day -&gt; BBL/DAY</v>
+        <v>bbl/day -&gt; bbld</v>
       </c>
       <c r="C1828" t="s">
         <v>883</v>
       </c>
       <c r="D1828" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="E1828">
         <v>1</v>
@@ -42276,13 +42294,13 @@
       </c>
       <c r="B1829" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bbld -&gt; bbl/day</v>
+        <v>bbl/day -&gt; BBL/DAY</v>
       </c>
       <c r="C1829" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D1829" t="s">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="E1829">
         <v>1</v>
@@ -42297,13 +42315,13 @@
       </c>
       <c r="B1830" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bbld -&gt; BBLD</v>
+        <v>bbld -&gt; bbl/day</v>
       </c>
       <c r="C1830" t="s">
         <v>884</v>
       </c>
       <c r="D1830" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="E1830">
         <v>1</v>
@@ -42318,13 +42336,13 @@
       </c>
       <c r="B1831" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>m3/day -&gt; m3/d</v>
+        <v>bbld -&gt; BBLD</v>
       </c>
       <c r="C1831" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D1831" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="E1831">
         <v>1</v>
@@ -42339,13 +42357,13 @@
       </c>
       <c r="B1832" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>m3/day -&gt; M3/DAY</v>
+        <v>m3/day -&gt; m3/d</v>
       </c>
       <c r="C1832" t="s">
         <v>885</v>
       </c>
       <c r="D1832" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="E1832">
         <v>1</v>
@@ -42360,13 +42378,13 @@
       </c>
       <c r="B1833" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>m3/d -&gt; m3/day</v>
+        <v>m3/day -&gt; M3/DAY</v>
       </c>
       <c r="C1833" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D1833" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="E1833">
         <v>1</v>
@@ -42381,13 +42399,13 @@
       </c>
       <c r="B1834" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>m3/d -&gt; M3/D</v>
+        <v>m3/d -&gt; m3/day</v>
       </c>
       <c r="C1834" t="s">
         <v>886</v>
       </c>
       <c r="D1834" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="E1834">
         <v>1</v>
@@ -42402,13 +42420,13 @@
       </c>
       <c r="B1835" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>ft3/day -&gt; cf/day</v>
+        <v>m3/d -&gt; M3/D</v>
       </c>
       <c r="C1835" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D1835" t="s">
-        <v>878</v>
+        <v>900</v>
       </c>
       <c r="E1835">
         <v>1</v>
@@ -42423,13 +42441,13 @@
       </c>
       <c r="B1836" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>ft3/day -&gt; FT3/DAY</v>
+        <v>ft3/day -&gt; cf/day</v>
       </c>
       <c r="C1836" t="s">
         <v>887</v>
       </c>
       <c r="D1836" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
       <c r="E1836">
         <v>1</v>
@@ -42444,13 +42462,13 @@
       </c>
       <c r="B1837" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>STB/DAY -&gt; stb/day</v>
+        <v>ft3/day -&gt; FT3/DAY</v>
       </c>
       <c r="C1837" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D1837" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="E1837">
         <v>1</v>
@@ -42465,13 +42483,13 @@
       </c>
       <c r="B1838" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>STBD -&gt; stbd</v>
+        <v>STB/DAY -&gt; stb/day</v>
       </c>
       <c r="C1838" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D1838" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E1838">
         <v>1</v>
@@ -42486,13 +42504,13 @@
       </c>
       <c r="B1839" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>SCF/DAY -&gt; scf/day</v>
+        <v>STBD -&gt; stbd</v>
       </c>
       <c r="C1839" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D1839" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E1839">
         <v>1</v>
@@ -42507,13 +42525,13 @@
       </c>
       <c r="B1840" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>SCFD -&gt; scfd</v>
+        <v>SCF/DAY -&gt; scf/day</v>
       </c>
       <c r="C1840" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D1840" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E1840">
         <v>1</v>
@@ -42528,13 +42546,13 @@
       </c>
       <c r="B1841" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>CF/DAY -&gt; cf/day</v>
+        <v>SCFD -&gt; scfd</v>
       </c>
       <c r="C1841" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D1841" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E1841">
         <v>1</v>
@@ -42549,13 +42567,13 @@
       </c>
       <c r="B1842" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>SM3/DAY -&gt; sm3/day</v>
+        <v>CF/DAY -&gt; cf/day</v>
       </c>
       <c r="C1842" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D1842" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E1842">
         <v>1</v>
@@ -42570,13 +42588,13 @@
       </c>
       <c r="B1843" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>SM3D -&gt; sm3d</v>
+        <v>SM3/DAY -&gt; sm3/day</v>
       </c>
       <c r="C1843" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D1843" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E1843">
         <v>1</v>
@@ -42591,13 +42609,13 @@
       </c>
       <c r="B1844" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>STM3D -&gt; stm3d</v>
+        <v>SM3D -&gt; sm3d</v>
       </c>
       <c r="C1844" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D1844" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E1844">
         <v>1</v>
@@ -42612,13 +42630,13 @@
       </c>
       <c r="B1845" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>STM3/DAY -&gt; stm3/day</v>
+        <v>STM3D -&gt; stm3d</v>
       </c>
       <c r="C1845" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D1845" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E1845">
         <v>1</v>
@@ -42633,13 +42651,13 @@
       </c>
       <c r="B1846" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>BBL/DAY -&gt; bbl/day</v>
+        <v>STM3/DAY -&gt; stm3/day</v>
       </c>
       <c r="C1846" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D1846" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E1846">
         <v>1</v>
@@ -42654,13 +42672,13 @@
       </c>
       <c r="B1847" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>BBLD -&gt; bbld</v>
+        <v>BBL/DAY -&gt; bbl/day</v>
       </c>
       <c r="C1847" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D1847" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E1847">
         <v>1</v>
@@ -42675,13 +42693,13 @@
       </c>
       <c r="B1848" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>M3/DAY -&gt; m3/day</v>
+        <v>BBLD -&gt; bbld</v>
       </c>
       <c r="C1848" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D1848" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E1848">
         <v>1</v>
@@ -42696,13 +42714,13 @@
       </c>
       <c r="B1849" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>M3/D -&gt; m3/d</v>
+        <v>M3/DAY -&gt; m3/day</v>
       </c>
       <c r="C1849" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D1849" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E1849">
         <v>1</v>
@@ -42717,13 +42735,13 @@
       </c>
       <c r="B1850" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>FT3/DAY -&gt; ft3/day</v>
+        <v>M3/D -&gt; m3/d</v>
       </c>
       <c r="C1850" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D1850" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E1850">
         <v>1</v>
@@ -42738,13 +42756,13 @@
       </c>
       <c r="B1851" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bit -&gt; b</v>
+        <v>FT3/DAY -&gt; ft3/day</v>
       </c>
       <c r="C1851" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D1851" t="s">
-        <v>1120</v>
+        <v>887</v>
       </c>
       <c r="E1851">
         <v>1</v>
@@ -42759,13 +42777,13 @@
       </c>
       <c r="B1852" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>b -&gt; bit</v>
+        <v>bit -&gt; b</v>
       </c>
       <c r="C1852" t="s">
+        <v>906</v>
+      </c>
+      <c r="D1852" t="s">
         <v>1120</v>
-      </c>
-      <c r="D1852" t="s">
-        <v>906</v>
       </c>
       <c r="E1852">
         <v>1</v>
@@ -42780,13 +42798,13 @@
       </c>
       <c r="B1853" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bit -&gt; BIT</v>
+        <v>b -&gt; bit</v>
       </c>
       <c r="C1853" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D1853" t="s">
         <v>906</v>
-      </c>
-      <c r="D1853" t="s">
-        <v>1121</v>
       </c>
       <c r="E1853">
         <v>1</v>
@@ -42801,13 +42819,13 @@
       </c>
       <c r="B1854" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>BIT -&gt; bit</v>
+        <v>bit -&gt; BIT</v>
       </c>
       <c r="C1854" t="s">
+        <v>906</v>
+      </c>
+      <c r="D1854" t="s">
         <v>1121</v>
-      </c>
-      <c r="D1854" t="s">
-        <v>906</v>
       </c>
       <c r="E1854">
         <v>1</v>
@@ -42822,13 +42840,13 @@
       </c>
       <c r="B1855" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>b -&gt; BIT</v>
+        <v>BIT -&gt; bit</v>
       </c>
       <c r="C1855" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D1855" t="s">
-        <v>1121</v>
+        <v>906</v>
       </c>
       <c r="E1855">
         <v>1</v>
@@ -42843,13 +42861,13 @@
       </c>
       <c r="B1856" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>BIT -&gt; b</v>
+        <v>b -&gt; BIT</v>
       </c>
       <c r="C1856" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D1856" t="s">
         <v>1121</v>
-      </c>
-      <c r="D1856" t="s">
-        <v>1120</v>
       </c>
       <c r="E1856">
         <v>1</v>
@@ -42864,13 +42882,13 @@
       </c>
       <c r="B1857" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>byte -&gt; B</v>
+        <v>BIT -&gt; b</v>
       </c>
       <c r="C1857" t="s">
-        <v>905</v>
+        <v>1121</v>
       </c>
       <c r="D1857" t="s">
-        <v>902</v>
+        <v>1120</v>
       </c>
       <c r="E1857">
         <v>1</v>
@@ -42885,13 +42903,13 @@
       </c>
       <c r="B1858" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>B -&gt; byte</v>
+        <v>byte -&gt; B</v>
       </c>
       <c r="C1858" t="s">
+        <v>905</v>
+      </c>
+      <c r="D1858" t="s">
         <v>902</v>
-      </c>
-      <c r="D1858" t="s">
-        <v>905</v>
       </c>
       <c r="E1858">
         <v>1</v>
@@ -42906,13 +42924,13 @@
       </c>
       <c r="B1859" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>byte -&gt; Byte</v>
+        <v>B -&gt; byte</v>
       </c>
       <c r="C1859" t="s">
+        <v>902</v>
+      </c>
+      <c r="D1859" t="s">
         <v>905</v>
-      </c>
-      <c r="D1859" t="s">
-        <v>903</v>
       </c>
       <c r="E1859">
         <v>1</v>
@@ -42927,13 +42945,13 @@
       </c>
       <c r="B1860" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Byte -&gt; byte</v>
+        <v>byte -&gt; Byte</v>
       </c>
       <c r="C1860" t="s">
+        <v>905</v>
+      </c>
+      <c r="D1860" t="s">
         <v>903</v>
-      </c>
-      <c r="D1860" t="s">
-        <v>905</v>
       </c>
       <c r="E1860">
         <v>1</v>
@@ -42948,13 +42966,13 @@
       </c>
       <c r="B1861" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>byte -&gt; BYTE</v>
+        <v>Byte -&gt; byte</v>
       </c>
       <c r="C1861" t="s">
+        <v>903</v>
+      </c>
+      <c r="D1861" t="s">
         <v>905</v>
-      </c>
-      <c r="D1861" t="s">
-        <v>904</v>
       </c>
       <c r="E1861">
         <v>1</v>
@@ -42969,13 +42987,13 @@
       </c>
       <c r="B1862" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>BYTE -&gt; byte</v>
+        <v>byte -&gt; BYTE</v>
       </c>
       <c r="C1862" t="s">
+        <v>905</v>
+      </c>
+      <c r="D1862" t="s">
         <v>904</v>
-      </c>
-      <c r="D1862" t="s">
-        <v>905</v>
       </c>
       <c r="E1862">
         <v>1</v>
@@ -42990,13 +43008,13 @@
       </c>
       <c r="B1863" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Byte -&gt; BYTE</v>
+        <v>BYTE -&gt; byte</v>
       </c>
       <c r="C1863" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D1863" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E1863">
         <v>1</v>
@@ -43011,13 +43029,13 @@
       </c>
       <c r="B1864" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>BYTE -&gt; Byte</v>
+        <v>Byte -&gt; BYTE</v>
       </c>
       <c r="C1864" t="s">
+        <v>903</v>
+      </c>
+      <c r="D1864" t="s">
         <v>904</v>
-      </c>
-      <c r="D1864" t="s">
-        <v>903</v>
       </c>
       <c r="E1864">
         <v>1</v>
@@ -43032,19 +43050,19 @@
       </c>
       <c r="B1865" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>byte -&gt; bit</v>
+        <v>BYTE -&gt; Byte</v>
       </c>
       <c r="C1865" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D1865" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="E1865">
         <v>1</v>
       </c>
       <c r="F1865">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1866" spans="1:6" x14ac:dyDescent="0.3">
@@ -43053,19 +43071,19 @@
       </c>
       <c r="B1866" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>bit -&gt; byte</v>
+        <v>byte -&gt; bit</v>
       </c>
       <c r="C1866" t="s">
+        <v>905</v>
+      </c>
+      <c r="D1866" t="s">
         <v>906</v>
       </c>
-      <c r="D1866" t="s">
-        <v>905</v>
-      </c>
       <c r="E1866">
         <v>1</v>
       </c>
       <c r="F1866">
-        <v>0.125</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1867" spans="1:6" x14ac:dyDescent="0.3">
@@ -43074,19 +43092,19 @@
       </c>
       <c r="B1867" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>centipoise -&gt; cP</v>
+        <v>bit -&gt; byte</v>
       </c>
       <c r="C1867" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D1867" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="E1867">
         <v>1</v>
       </c>
       <c r="F1867">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="1868" spans="1:6" x14ac:dyDescent="0.3">
@@ -43095,13 +43113,13 @@
       </c>
       <c r="B1868" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>centipoise -&gt; CENTIPOISE</v>
+        <v>centipoise -&gt; cP</v>
       </c>
       <c r="C1868" t="s">
         <v>907</v>
       </c>
       <c r="D1868" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="E1868">
         <v>1</v>
@@ -43116,13 +43134,13 @@
       </c>
       <c r="B1869" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>cP -&gt; centipoise</v>
+        <v>centipoise -&gt; CENTIPOISE</v>
       </c>
       <c r="C1869" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D1869" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="E1869">
         <v>1</v>
@@ -43137,13 +43155,13 @@
       </c>
       <c r="B1870" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Poise -&gt; dyne*s/cm2</v>
+        <v>cP -&gt; centipoise</v>
       </c>
       <c r="C1870" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D1870" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="E1870">
         <v>1</v>
@@ -43158,13 +43176,13 @@
       </c>
       <c r="B1871" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Poise -&gt; g/cm/s</v>
+        <v>Poise -&gt; dyne*s/cm2</v>
       </c>
       <c r="C1871" t="s">
         <v>909</v>
       </c>
       <c r="D1871" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E1871">
         <v>1</v>
@@ -43179,13 +43197,13 @@
       </c>
       <c r="B1872" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Poise -&gt; POISE</v>
+        <v>Poise -&gt; g/cm/s</v>
       </c>
       <c r="C1872" t="s">
         <v>909</v>
       </c>
       <c r="D1872" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="E1872">
         <v>1</v>
@@ -43200,19 +43218,19 @@
       </c>
       <c r="B1873" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Poise -&gt; Pa*s</v>
+        <v>Poise -&gt; POISE</v>
       </c>
       <c r="C1873" t="s">
         <v>909</v>
       </c>
       <c r="D1873" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="E1873">
         <v>1</v>
       </c>
       <c r="F1873">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1874" spans="1:6" x14ac:dyDescent="0.3">
@@ -43221,19 +43239,19 @@
       </c>
       <c r="B1874" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>dyne*s/cm2 -&gt; Poise</v>
+        <v>Poise -&gt; Pa*s</v>
       </c>
       <c r="C1874" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D1874" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E1874">
         <v>1</v>
       </c>
       <c r="F1874">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1875" spans="1:6" x14ac:dyDescent="0.3">
@@ -43242,13 +43260,13 @@
       </c>
       <c r="B1875" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>dyne*s/cm2 -&gt; DYNE*S/CM2</v>
+        <v>dyne*s/cm2 -&gt; Poise</v>
       </c>
       <c r="C1875" t="s">
         <v>910</v>
       </c>
       <c r="D1875" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="E1875">
         <v>1</v>
@@ -43263,13 +43281,13 @@
       </c>
       <c r="B1876" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>g/cm/s -&gt; Poise</v>
+        <v>dyne*s/cm2 -&gt; DYNE*S/CM2</v>
       </c>
       <c r="C1876" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D1876" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="E1876">
         <v>1</v>
@@ -43284,13 +43302,13 @@
       </c>
       <c r="B1877" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>g/cm/s -&gt; G/CM/S</v>
+        <v>g/cm/s -&gt; Poise</v>
       </c>
       <c r="C1877" t="s">
         <v>911</v>
       </c>
       <c r="D1877" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="E1877">
         <v>1</v>
@@ -43305,13 +43323,13 @@
       </c>
       <c r="B1878" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Pa*s -&gt; N*s/m2</v>
+        <v>g/cm/s -&gt; G/CM/S</v>
       </c>
       <c r="C1878" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D1878" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="E1878">
         <v>1</v>
@@ -43326,13 +43344,13 @@
       </c>
       <c r="B1879" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Pa*s -&gt; kg/m/s</v>
+        <v>Pa*s -&gt; N*s/m2</v>
       </c>
       <c r="C1879" t="s">
         <v>912</v>
       </c>
       <c r="D1879" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E1879">
         <v>1</v>
@@ -43347,13 +43365,13 @@
       </c>
       <c r="B1880" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Pa*s -&gt; PA*S</v>
+        <v>Pa*s -&gt; kg/m/s</v>
       </c>
       <c r="C1880" t="s">
         <v>912</v>
       </c>
       <c r="D1880" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="E1880">
         <v>1</v>
@@ -43368,19 +43386,19 @@
       </c>
       <c r="B1881" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>Pa*s -&gt; Poise</v>
+        <v>Pa*s -&gt; PA*S</v>
       </c>
       <c r="C1881" t="s">
         <v>912</v>
       </c>
       <c r="D1881" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="E1881">
         <v>1</v>
       </c>
       <c r="F1881">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1882" spans="1:6" x14ac:dyDescent="0.3">
@@ -43389,19 +43407,19 @@
       </c>
       <c r="B1882" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>N*s/m2 -&gt; Pa*s</v>
+        <v>Pa*s -&gt; Poise</v>
       </c>
       <c r="C1882" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D1882" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="E1882">
         <v>1</v>
       </c>
       <c r="F1882">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1883" spans="1:6" x14ac:dyDescent="0.3">
@@ -43410,13 +43428,13 @@
       </c>
       <c r="B1883" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>N*s/m2 -&gt; N*S/M2</v>
+        <v>N*s/m2 -&gt; Pa*s</v>
       </c>
       <c r="C1883" t="s">
         <v>913</v>
       </c>
       <c r="D1883" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="E1883">
         <v>1</v>
@@ -43431,13 +43449,13 @@
       </c>
       <c r="B1884" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>kg/m/s -&gt; Pa*s</v>
+        <v>N*s/m2 -&gt; N*S/M2</v>
       </c>
       <c r="C1884" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D1884" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="E1884">
         <v>1</v>
@@ -43452,13 +43470,13 @@
       </c>
       <c r="B1885" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>kg/m/s -&gt; KG/M/S</v>
+        <v>kg/m/s -&gt; Pa*s</v>
       </c>
       <c r="C1885" t="s">
         <v>914</v>
       </c>
       <c r="D1885" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="E1885">
         <v>1</v>
@@ -43473,13 +43491,13 @@
       </c>
       <c r="B1886" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>CENTIPOISE -&gt; centipoise</v>
+        <v>kg/m/s -&gt; KG/M/S</v>
       </c>
       <c r="C1886" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D1886" t="s">
-        <v>907</v>
+        <v>921</v>
       </c>
       <c r="E1886">
         <v>1</v>
@@ -43494,13 +43512,13 @@
       </c>
       <c r="B1887" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>POISE -&gt; Poise</v>
+        <v>CENTIPOISE -&gt; centipoise</v>
       </c>
       <c r="C1887" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D1887" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E1887">
         <v>1</v>
@@ -43515,13 +43533,13 @@
       </c>
       <c r="B1888" s="2" t="str">
         <f t="shared" si="29"/>
-        <v>DYNE*S/CM2 -&gt; dyne*s/cm2</v>
+        <v>POISE -&gt; Poise</v>
       </c>
       <c r="C1888" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D1888" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1888">
         <v>1</v>
@@ -43535,14 +43553,14 @@
         <v>1887</v>
       </c>
       <c r="B1889" s="2" t="str">
-        <f t="shared" ref="B1889:B1952" si="30">C1889&amp;" -&gt; " &amp;D1889</f>
-        <v>G/CM/S -&gt; g/cm/s</v>
+        <f t="shared" si="29"/>
+        <v>DYNE*S/CM2 -&gt; dyne*s/cm2</v>
       </c>
       <c r="C1889" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D1889" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E1889">
         <v>1</v>
@@ -43556,14 +43574,14 @@
         <v>1888</v>
       </c>
       <c r="B1890" s="2" t="str">
-        <f t="shared" si="30"/>
-        <v>PA*S -&gt; Pa*s</v>
+        <f t="shared" ref="B1890:B1953" si="30">C1890&amp;" -&gt; " &amp;D1890</f>
+        <v>G/CM/S -&gt; g/cm/s</v>
       </c>
       <c r="C1890" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D1890" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E1890">
         <v>1</v>
@@ -43578,13 +43596,13 @@
       </c>
       <c r="B1891" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>N*S/M2 -&gt; N*s/m2</v>
+        <v>PA*S -&gt; Pa*s</v>
       </c>
       <c r="C1891" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D1891" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E1891">
         <v>1</v>
@@ -43599,13 +43617,13 @@
       </c>
       <c r="B1892" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>KG/M/S -&gt; kg/m/s</v>
+        <v>N*S/M2 -&gt; N*s/m2</v>
       </c>
       <c r="C1892" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D1892" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E1892">
         <v>1</v>
@@ -43620,13 +43638,13 @@
       </c>
       <c r="B1893" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Darcy -&gt; DARCY</v>
+        <v>KG/M/S -&gt; kg/m/s</v>
       </c>
       <c r="C1893" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D1893" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="E1893">
         <v>1</v>
@@ -43641,19 +43659,19 @@
       </c>
       <c r="B1894" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Darcy -&gt; µm2</v>
+        <v>Darcy -&gt; DARCY</v>
       </c>
       <c r="C1894" t="s">
         <v>922</v>
       </c>
       <c r="D1894" t="s">
-        <v>229</v>
+        <v>923</v>
       </c>
       <c r="E1894">
         <v>1</v>
       </c>
       <c r="F1894">
-        <v>0.98692329999999995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1895" spans="1:6" x14ac:dyDescent="0.3">
@@ -43662,19 +43680,19 @@
       </c>
       <c r="B1895" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>DARCY -&gt; Darcy</v>
+        <v>Darcy -&gt; µm2</v>
       </c>
       <c r="C1895" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D1895" t="s">
-        <v>922</v>
+        <v>229</v>
       </c>
       <c r="E1895">
         <v>1</v>
       </c>
       <c r="F1895">
-        <v>1</v>
+        <v>0.98692329999999995</v>
       </c>
     </row>
     <row r="1896" spans="1:6" x14ac:dyDescent="0.3">
@@ -43683,13 +43701,13 @@
       </c>
       <c r="B1896" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Newton -&gt; N</v>
+        <v>DARCY -&gt; Darcy</v>
       </c>
       <c r="C1896" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D1896" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="E1896">
         <v>1</v>
@@ -43704,13 +43722,13 @@
       </c>
       <c r="B1897" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Newton -&gt; newton</v>
+        <v>Newton -&gt; N</v>
       </c>
       <c r="C1897" t="s">
         <v>924</v>
       </c>
       <c r="D1897" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E1897">
         <v>1</v>
@@ -43725,13 +43743,13 @@
       </c>
       <c r="B1898" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Newton -&gt; kg*m/s2</v>
+        <v>Newton -&gt; newton</v>
       </c>
       <c r="C1898" t="s">
         <v>924</v>
       </c>
       <c r="D1898" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E1898">
         <v>1</v>
@@ -43746,13 +43764,13 @@
       </c>
       <c r="B1899" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Newton -&gt; NEWTON</v>
+        <v>Newton -&gt; kg*m/s2</v>
       </c>
       <c r="C1899" t="s">
         <v>924</v>
       </c>
       <c r="D1899" t="s">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="E1899">
         <v>1</v>
@@ -43767,19 +43785,19 @@
       </c>
       <c r="B1900" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Newton -&gt; Dyne</v>
+        <v>Newton -&gt; NEWTON</v>
       </c>
       <c r="C1900" t="s">
         <v>924</v>
       </c>
       <c r="D1900" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="E1900">
         <v>1</v>
       </c>
       <c r="F1900">
-        <v>100000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1901" spans="1:6" x14ac:dyDescent="0.3">
@@ -43788,19 +43806,19 @@
       </c>
       <c r="B1901" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>N -&gt; Newton</v>
+        <v>Newton -&gt; Dyne</v>
       </c>
       <c r="C1901" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D1901" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="E1901">
         <v>1</v>
       </c>
       <c r="F1901">
-        <v>1</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="1902" spans="1:6" x14ac:dyDescent="0.3">
@@ -43809,13 +43827,13 @@
       </c>
       <c r="B1902" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>N -&gt; N</v>
+        <v>N -&gt; Newton</v>
       </c>
       <c r="C1902" t="s">
         <v>925</v>
       </c>
       <c r="D1902" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E1902">
         <v>1</v>
@@ -43830,13 +43848,13 @@
       </c>
       <c r="B1903" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>newton -&gt; Newton</v>
+        <v>N -&gt; N</v>
       </c>
       <c r="C1903" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D1903" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E1903">
         <v>1</v>
@@ -43851,13 +43869,13 @@
       </c>
       <c r="B1904" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>newton -&gt; NEWTON</v>
+        <v>newton -&gt; Newton</v>
       </c>
       <c r="C1904" t="s">
         <v>926</v>
       </c>
       <c r="D1904" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="E1904">
         <v>1</v>
@@ -43872,13 +43890,13 @@
       </c>
       <c r="B1905" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kg*m/s2 -&gt; Newton</v>
+        <v>newton -&gt; NEWTON</v>
       </c>
       <c r="C1905" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D1905" t="s">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="E1905">
         <v>1</v>
@@ -43893,13 +43911,13 @@
       </c>
       <c r="B1906" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kg*m/s2 -&gt; KG*M/S2</v>
+        <v>kg*m/s2 -&gt; Newton</v>
       </c>
       <c r="C1906" t="s">
         <v>927</v>
       </c>
       <c r="D1906" t="s">
-        <v>938</v>
+        <v>924</v>
       </c>
       <c r="E1906">
         <v>1</v>
@@ -43914,13 +43932,13 @@
       </c>
       <c r="B1907" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilogram force -&gt; kgf</v>
+        <v>kg*m/s2 -&gt; KG*M/S2</v>
       </c>
       <c r="C1907" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D1907" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="E1907">
         <v>1</v>
@@ -43935,13 +43953,13 @@
       </c>
       <c r="B1908" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilogram force -&gt; kilopondio</v>
+        <v>kilogram force -&gt; kgf</v>
       </c>
       <c r="C1908" t="s">
         <v>928</v>
       </c>
       <c r="D1908" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E1908">
         <v>1</v>
@@ -43956,19 +43974,19 @@
       </c>
       <c r="B1909" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilogram force -&gt; kilogram mass</v>
+        <v>kilogram force -&gt; kilopondio</v>
       </c>
       <c r="C1909" t="s">
         <v>928</v>
       </c>
       <c r="D1909" t="s">
-        <v>830</v>
+        <v>930</v>
       </c>
       <c r="E1909">
         <v>1</v>
       </c>
       <c r="F1909">
-        <v>0.1019716212977928</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1910" spans="1:6" x14ac:dyDescent="0.3">
@@ -43977,19 +43995,19 @@
       </c>
       <c r="B1910" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilogram force -&gt; kilogram-force</v>
+        <v>kilogram force -&gt; kilogram mass</v>
       </c>
       <c r="C1910" t="s">
         <v>928</v>
       </c>
       <c r="D1910" t="s">
-        <v>936</v>
+        <v>830</v>
       </c>
       <c r="E1910">
         <v>1</v>
       </c>
       <c r="F1910">
-        <v>1</v>
+        <v>0.1019716212977928</v>
       </c>
     </row>
     <row r="1911" spans="1:6" x14ac:dyDescent="0.3">
@@ -43998,13 +44016,13 @@
       </c>
       <c r="B1911" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilogram force -&gt; KILOGRAM FORCE</v>
+        <v>kilogram force -&gt; kilogram-force</v>
       </c>
       <c r="C1911" t="s">
         <v>928</v>
       </c>
       <c r="D1911" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="E1911">
         <v>1</v>
@@ -44019,13 +44037,13 @@
       </c>
       <c r="B1912" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kgf -&gt; kilogram force</v>
+        <v>kilogram force -&gt; KILOGRAM FORCE</v>
       </c>
       <c r="C1912" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D1912" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="E1912">
         <v>1</v>
@@ -44040,13 +44058,13 @@
       </c>
       <c r="B1913" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kgf -&gt; KGF</v>
+        <v>kgf -&gt; kilogram force</v>
       </c>
       <c r="C1913" t="s">
         <v>929</v>
       </c>
       <c r="D1913" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="E1913">
         <v>1</v>
@@ -44061,13 +44079,13 @@
       </c>
       <c r="B1914" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilopondio -&gt; kilogram force</v>
+        <v>kgf -&gt; KGF</v>
       </c>
       <c r="C1914" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D1914" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="E1914">
         <v>1</v>
@@ -44082,13 +44100,13 @@
       </c>
       <c r="B1915" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilopondio -&gt; kp</v>
+        <v>kilopondio -&gt; kilogram force</v>
       </c>
       <c r="C1915" t="s">
         <v>930</v>
       </c>
       <c r="D1915" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="E1915">
         <v>1</v>
@@ -44103,13 +44121,13 @@
       </c>
       <c r="B1916" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilopondio -&gt; KILOPONDIO</v>
+        <v>kilopondio -&gt; kp</v>
       </c>
       <c r="C1916" t="s">
         <v>930</v>
       </c>
       <c r="D1916" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
       <c r="E1916">
         <v>1</v>
@@ -44124,13 +44142,13 @@
       </c>
       <c r="B1917" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kp -&gt; kilopondio</v>
+        <v>kilopondio -&gt; KILOPONDIO</v>
       </c>
       <c r="C1917" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D1917" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="E1917">
         <v>1</v>
@@ -44145,13 +44163,13 @@
       </c>
       <c r="B1918" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kp -&gt; KP</v>
+        <v>kp -&gt; kilopondio</v>
       </c>
       <c r="C1918" t="s">
         <v>931</v>
       </c>
       <c r="D1918" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="E1918">
         <v>1</v>
@@ -44166,13 +44184,13 @@
       </c>
       <c r="B1919" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Dyne -&gt; dyne</v>
+        <v>kp -&gt; KP</v>
       </c>
       <c r="C1919" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D1919" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="E1919">
         <v>1</v>
@@ -44187,13 +44205,13 @@
       </c>
       <c r="B1920" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Dyne -&gt; dyn</v>
+        <v>Dyne -&gt; dyne</v>
       </c>
       <c r="C1920" t="s">
         <v>932</v>
       </c>
       <c r="D1920" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E1920">
         <v>1</v>
@@ -44208,13 +44226,13 @@
       </c>
       <c r="B1921" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Dyne -&gt; g*cm/s2</v>
+        <v>Dyne -&gt; dyn</v>
       </c>
       <c r="C1921" t="s">
         <v>932</v>
       </c>
       <c r="D1921" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E1921">
         <v>1</v>
@@ -44229,13 +44247,13 @@
       </c>
       <c r="B1922" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Dyne -&gt; DYNE</v>
+        <v>Dyne -&gt; g*cm/s2</v>
       </c>
       <c r="C1922" t="s">
         <v>932</v>
       </c>
       <c r="D1922" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="E1922">
         <v>1</v>
@@ -44250,19 +44268,19 @@
       </c>
       <c r="B1923" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>Dyne -&gt; Newton</v>
+        <v>Dyne -&gt; DYNE</v>
       </c>
       <c r="C1923" t="s">
         <v>932</v>
       </c>
       <c r="D1923" t="s">
-        <v>924</v>
+        <v>943</v>
       </c>
       <c r="E1923">
         <v>1</v>
       </c>
       <c r="F1923">
-        <v>1.0000000000000001E-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1924" spans="1:6" x14ac:dyDescent="0.3">
@@ -44271,19 +44289,19 @@
       </c>
       <c r="B1924" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>dyne -&gt; Dyne</v>
+        <v>Dyne -&gt; Newton</v>
       </c>
       <c r="C1924" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D1924" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="E1924">
         <v>1</v>
       </c>
       <c r="F1924">
-        <v>1</v>
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="1925" spans="1:6" x14ac:dyDescent="0.3">
@@ -44292,13 +44310,13 @@
       </c>
       <c r="B1925" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>dyne -&gt; DYNE</v>
+        <v>dyne -&gt; Dyne</v>
       </c>
       <c r="C1925" t="s">
         <v>933</v>
       </c>
       <c r="D1925" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="E1925">
         <v>1</v>
@@ -44313,13 +44331,13 @@
       </c>
       <c r="B1926" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>dyn -&gt; Dyne</v>
+        <v>dyne -&gt; DYNE</v>
       </c>
       <c r="C1926" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D1926" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="E1926">
         <v>1</v>
@@ -44334,13 +44352,13 @@
       </c>
       <c r="B1927" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>dyn -&gt; DYN</v>
+        <v>dyn -&gt; Dyne</v>
       </c>
       <c r="C1927" t="s">
         <v>934</v>
       </c>
       <c r="D1927" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="E1927">
         <v>1</v>
@@ -44355,13 +44373,13 @@
       </c>
       <c r="B1928" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>g*cm/s2 -&gt; Dyne</v>
+        <v>dyn -&gt; DYN</v>
       </c>
       <c r="C1928" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D1928" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="E1928">
         <v>1</v>
@@ -44376,13 +44394,13 @@
       </c>
       <c r="B1929" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>g*cm/s2 -&gt; G*CM/S2</v>
+        <v>g*cm/s2 -&gt; Dyne</v>
       </c>
       <c r="C1929" t="s">
         <v>935</v>
       </c>
       <c r="D1929" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="E1929">
         <v>1</v>
@@ -44397,13 +44415,13 @@
       </c>
       <c r="B1930" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>kilogram-force -&gt; kilogram force</v>
+        <v>g*cm/s2 -&gt; G*CM/S2</v>
       </c>
       <c r="C1930" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D1930" t="s">
-        <v>928</v>
+        <v>945</v>
       </c>
       <c r="E1930">
         <v>1</v>
@@ -44418,13 +44436,13 @@
       </c>
       <c r="B1931" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>NEWTON -&gt; Newton</v>
+        <v>kilogram-force -&gt; kilogram force</v>
       </c>
       <c r="C1931" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D1931" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="E1931">
         <v>1</v>
@@ -44439,13 +44457,13 @@
       </c>
       <c r="B1932" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>NEWTON -&gt; newton</v>
+        <v>NEWTON -&gt; Newton</v>
       </c>
       <c r="C1932" t="s">
         <v>937</v>
       </c>
       <c r="D1932" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="E1932">
         <v>1</v>
@@ -44460,13 +44478,13 @@
       </c>
       <c r="B1933" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>KG*M/S2 -&gt; kg*m/s2</v>
+        <v>NEWTON -&gt; newton</v>
       </c>
       <c r="C1933" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D1933" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E1933">
         <v>1</v>
@@ -44481,13 +44499,13 @@
       </c>
       <c r="B1934" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>KILOGRAM FORCE -&gt; kilogram force</v>
+        <v>KG*M/S2 -&gt; kg*m/s2</v>
       </c>
       <c r="C1934" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D1934" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E1934">
         <v>1</v>
@@ -44502,13 +44520,13 @@
       </c>
       <c r="B1935" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>KGF -&gt; kgf</v>
+        <v>KILOGRAM FORCE -&gt; kilogram force</v>
       </c>
       <c r="C1935" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D1935" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E1935">
         <v>1</v>
@@ -44523,13 +44541,13 @@
       </c>
       <c r="B1936" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>KILOPONDIO -&gt; kilopondio</v>
+        <v>KGF -&gt; kgf</v>
       </c>
       <c r="C1936" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D1936" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E1936">
         <v>1</v>
@@ -44544,13 +44562,13 @@
       </c>
       <c r="B1937" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>KP -&gt; kp</v>
+        <v>KILOPONDIO -&gt; kilopondio</v>
       </c>
       <c r="C1937" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D1937" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E1937">
         <v>1</v>
@@ -44565,13 +44583,13 @@
       </c>
       <c r="B1938" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>DYNE -&gt; Dyne</v>
+        <v>KP -&gt; kp</v>
       </c>
       <c r="C1938" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D1938" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E1938">
         <v>1</v>
@@ -44586,13 +44604,13 @@
       </c>
       <c r="B1939" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>DYNE -&gt; dyne</v>
+        <v>DYNE -&gt; Dyne</v>
       </c>
       <c r="C1939" t="s">
         <v>943</v>
       </c>
       <c r="D1939" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E1939">
         <v>1</v>
@@ -44607,13 +44625,13 @@
       </c>
       <c r="B1940" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>DYN -&gt; dyn</v>
+        <v>DYNE -&gt; dyne</v>
       </c>
       <c r="C1940" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D1940" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E1940">
         <v>1</v>
@@ -44628,13 +44646,13 @@
       </c>
       <c r="B1941" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>G*CM/S2 -&gt; g*cm/s2</v>
+        <v>DYN -&gt; dyn</v>
       </c>
       <c r="C1941" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D1941" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E1941">
         <v>1</v>
@@ -44649,13 +44667,13 @@
       </c>
       <c r="B1942" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; STB/DAY/</v>
+        <v>G*CM/S2 -&gt; g*cm/s2</v>
       </c>
       <c r="C1942" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D1942" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="E1942">
         <v>1</v>
@@ -44670,13 +44688,13 @@
       </c>
       <c r="B1943" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; stbd/psi</v>
+        <v>stb/day/psi -&gt; STB/DAY/</v>
       </c>
       <c r="C1943" t="s">
         <v>946</v>
       </c>
       <c r="D1943" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E1943">
         <v>1</v>
@@ -44691,13 +44709,13 @@
       </c>
       <c r="B1944" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; stbd/psia</v>
+        <v>stb/day/psi -&gt; stbd/psi</v>
       </c>
       <c r="C1944" t="s">
         <v>946</v>
       </c>
       <c r="D1944" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E1944">
         <v>1</v>
@@ -44712,13 +44730,13 @@
       </c>
       <c r="B1945" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; stb/day/psia</v>
+        <v>stb/day/psi -&gt; stbd/psia</v>
       </c>
       <c r="C1945" t="s">
         <v>946</v>
       </c>
       <c r="D1945" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E1945">
         <v>1</v>
@@ -44733,13 +44751,13 @@
       </c>
       <c r="B1946" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; stb/day-psi</v>
+        <v>stb/day/psi -&gt; stb/day/psia</v>
       </c>
       <c r="C1946" t="s">
         <v>946</v>
       </c>
       <c r="D1946" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E1946">
         <v>1</v>
@@ -44754,13 +44772,13 @@
       </c>
       <c r="B1947" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; stb/day-psia</v>
+        <v>stb/day/psi -&gt; stb/day-psi</v>
       </c>
       <c r="C1947" t="s">
         <v>946</v>
       </c>
       <c r="D1947" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E1947">
         <v>1</v>
@@ -44775,13 +44793,13 @@
       </c>
       <c r="B1948" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; stb/d/psi</v>
+        <v>stb/day/psi -&gt; stb/day-psia</v>
       </c>
       <c r="C1948" t="s">
         <v>946</v>
       </c>
       <c r="D1948" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E1948">
         <v>1</v>
@@ -44796,13 +44814,13 @@
       </c>
       <c r="B1949" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stb/day/psi -&gt; STB/DAY/PSI</v>
+        <v>stb/day/psi -&gt; stb/d/psi</v>
       </c>
       <c r="C1949" t="s">
         <v>946</v>
       </c>
       <c r="D1949" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="E1949">
         <v>1</v>
@@ -44817,13 +44835,13 @@
       </c>
       <c r="B1950" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>STB/DAY/ -&gt; stb/day/psi</v>
+        <v>stb/day/psi -&gt; STB/DAY/PSI</v>
       </c>
       <c r="C1950" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D1950" t="s">
-        <v>946</v>
+        <v>962</v>
       </c>
       <c r="E1950">
         <v>1</v>
@@ -44838,13 +44856,13 @@
       </c>
       <c r="B1951" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>STB/DAY/ -&gt; STB/DAY/</v>
+        <v>STB/DAY/ -&gt; stb/day/psi</v>
       </c>
       <c r="C1951" t="s">
         <v>947</v>
       </c>
       <c r="D1951" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E1951">
         <v>1</v>
@@ -44859,13 +44877,13 @@
       </c>
       <c r="B1952" s="2" t="str">
         <f t="shared" si="30"/>
-        <v>stbd/psi -&gt; stb/day/psi</v>
+        <v>STB/DAY/ -&gt; STB/DAY/</v>
       </c>
       <c r="C1952" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D1952" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E1952">
         <v>1</v>
@@ -44879,14 +44897,14 @@
         <v>1951</v>
       </c>
       <c r="B1953" s="2" t="str">
-        <f t="shared" ref="B1953:B2016" si="31">C1953&amp;" -&gt; " &amp;D1953</f>
-        <v>stbd/psi -&gt; STBD/PSI</v>
+        <f t="shared" si="30"/>
+        <v>stbd/psi -&gt; stb/day/psi</v>
       </c>
       <c r="C1953" t="s">
         <v>948</v>
       </c>
       <c r="D1953" t="s">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="E1953">
         <v>1</v>
@@ -44900,14 +44918,14 @@
         <v>1952</v>
       </c>
       <c r="B1954" s="2" t="str">
-        <f t="shared" si="31"/>
-        <v>stbd/psia -&gt; stb/day/psi</v>
+        <f t="shared" ref="B1954:B2017" si="31">C1954&amp;" -&gt; " &amp;D1954</f>
+        <v>stbd/psi -&gt; STBD/PSI</v>
       </c>
       <c r="C1954" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D1954" t="s">
-        <v>946</v>
+        <v>963</v>
       </c>
       <c r="E1954">
         <v>1</v>
@@ -44922,13 +44940,13 @@
       </c>
       <c r="B1955" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stbd/psia -&gt; STBD/PSIA</v>
+        <v>stbd/psia -&gt; stb/day/psi</v>
       </c>
       <c r="C1955" t="s">
         <v>949</v>
       </c>
       <c r="D1955" t="s">
-        <v>964</v>
+        <v>946</v>
       </c>
       <c r="E1955">
         <v>1</v>
@@ -44943,13 +44961,13 @@
       </c>
       <c r="B1956" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/day/psia -&gt; stb/day/psi</v>
+        <v>stbd/psia -&gt; STBD/PSIA</v>
       </c>
       <c r="C1956" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D1956" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="E1956">
         <v>1</v>
@@ -44964,13 +44982,13 @@
       </c>
       <c r="B1957" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/day/psia -&gt; STB/DAY/PSIA</v>
+        <v>stb/day/psia -&gt; stb/day/psi</v>
       </c>
       <c r="C1957" t="s">
         <v>950</v>
       </c>
       <c r="D1957" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="E1957">
         <v>1</v>
@@ -44985,13 +45003,13 @@
       </c>
       <c r="B1958" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/day-psi -&gt; stb/day/psi</v>
+        <v>stb/day/psia -&gt; STB/DAY/PSIA</v>
       </c>
       <c r="C1958" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D1958" t="s">
-        <v>946</v>
+        <v>965</v>
       </c>
       <c r="E1958">
         <v>1</v>
@@ -45006,13 +45024,13 @@
       </c>
       <c r="B1959" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/day-psi -&gt; STB/DAY-PSI</v>
+        <v>stb/day-psi -&gt; stb/day/psi</v>
       </c>
       <c r="C1959" t="s">
         <v>951</v>
       </c>
       <c r="D1959" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="E1959">
         <v>1</v>
@@ -45027,13 +45045,13 @@
       </c>
       <c r="B1960" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/day-psia -&gt; stb/day/psi</v>
+        <v>stb/day-psi -&gt; STB/DAY-PSI</v>
       </c>
       <c r="C1960" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D1960" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="E1960">
         <v>1</v>
@@ -45048,13 +45066,13 @@
       </c>
       <c r="B1961" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/day-psia -&gt; STB/DAY-PSIA</v>
+        <v>stb/day-psia -&gt; stb/day/psi</v>
       </c>
       <c r="C1961" t="s">
         <v>952</v>
       </c>
       <c r="D1961" t="s">
-        <v>967</v>
+        <v>946</v>
       </c>
       <c r="E1961">
         <v>1</v>
@@ -45069,13 +45087,13 @@
       </c>
       <c r="B1962" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/d/psi -&gt; stb/day/psi</v>
+        <v>stb/day-psia -&gt; STB/DAY-PSIA</v>
       </c>
       <c r="C1962" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D1962" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="E1962">
         <v>1</v>
@@ -45090,13 +45108,13 @@
       </c>
       <c r="B1963" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>stb/d/psi -&gt; STB/D/PSI</v>
+        <v>stb/d/psi -&gt; stb/day/psi</v>
       </c>
       <c r="C1963" t="s">
         <v>953</v>
       </c>
       <c r="D1963" t="s">
-        <v>968</v>
+        <v>946</v>
       </c>
       <c r="E1963">
         <v>1</v>
@@ -45111,13 +45129,13 @@
       </c>
       <c r="B1964" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; SM3/DAY/</v>
+        <v>stb/d/psi -&gt; STB/D/PSI</v>
       </c>
       <c r="C1964" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D1964" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="E1964">
         <v>1</v>
@@ -45132,13 +45150,13 @@
       </c>
       <c r="B1965" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; sm3/d/b</v>
+        <v>sm3/day/bar -&gt; SM3/DAY/</v>
       </c>
       <c r="C1965" t="s">
         <v>954</v>
       </c>
       <c r="D1965" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E1965">
         <v>1</v>
@@ -45153,13 +45171,13 @@
       </c>
       <c r="B1966" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; sm3d/bar</v>
+        <v>sm3/day/bar -&gt; sm3/d/b</v>
       </c>
       <c r="C1966" t="s">
         <v>954</v>
       </c>
       <c r="D1966" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E1966">
         <v>1</v>
@@ -45174,13 +45192,13 @@
       </c>
       <c r="B1967" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; sm3d/bara</v>
+        <v>sm3/day/bar -&gt; sm3d/bar</v>
       </c>
       <c r="C1967" t="s">
         <v>954</v>
       </c>
       <c r="D1967" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E1967">
         <v>1</v>
@@ -45195,13 +45213,13 @@
       </c>
       <c r="B1968" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; sm3/day/bara</v>
+        <v>sm3/day/bar -&gt; sm3d/bara</v>
       </c>
       <c r="C1968" t="s">
         <v>954</v>
       </c>
       <c r="D1968" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E1968">
         <v>1</v>
@@ -45216,13 +45234,13 @@
       </c>
       <c r="B1969" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; sm3/day-bar</v>
+        <v>sm3/day/bar -&gt; sm3/day/bara</v>
       </c>
       <c r="C1969" t="s">
         <v>954</v>
       </c>
       <c r="D1969" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E1969">
         <v>1</v>
@@ -45237,13 +45255,13 @@
       </c>
       <c r="B1970" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; sm3/day-bara</v>
+        <v>sm3/day/bar -&gt; sm3/day-bar</v>
       </c>
       <c r="C1970" t="s">
         <v>954</v>
       </c>
       <c r="D1970" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E1970">
         <v>1</v>
@@ -45258,13 +45276,13 @@
       </c>
       <c r="B1971" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bar -&gt; SM3/DAY/BAR</v>
+        <v>sm3/day/bar -&gt; sm3/day-bara</v>
       </c>
       <c r="C1971" t="s">
         <v>954</v>
       </c>
       <c r="D1971" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="E1971">
         <v>1</v>
@@ -45279,13 +45297,13 @@
       </c>
       <c r="B1972" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/ -&gt; sm3/day/bar</v>
+        <v>sm3/day/bar -&gt; SM3/DAY/BAR</v>
       </c>
       <c r="C1972" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D1972" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
       <c r="E1972">
         <v>1</v>
@@ -45300,13 +45318,13 @@
       </c>
       <c r="B1973" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/ -&gt; SM3/DAY/</v>
+        <v>SM3/DAY/ -&gt; sm3/day/bar</v>
       </c>
       <c r="C1973" t="s">
         <v>955</v>
       </c>
       <c r="D1973" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E1973">
         <v>1</v>
@@ -45321,13 +45339,13 @@
       </c>
       <c r="B1974" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/d/b -&gt; sm3/day/bar</v>
+        <v>SM3/DAY/ -&gt; SM3/DAY/</v>
       </c>
       <c r="C1974" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D1974" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E1974">
         <v>1</v>
@@ -45342,13 +45360,13 @@
       </c>
       <c r="B1975" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/d/b -&gt; SM3/D/B</v>
+        <v>sm3/d/b -&gt; sm3/day/bar</v>
       </c>
       <c r="C1975" t="s">
         <v>956</v>
       </c>
       <c r="D1975" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="E1975">
         <v>1</v>
@@ -45363,13 +45381,13 @@
       </c>
       <c r="B1976" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3d/bar -&gt; sm3/day/bar</v>
+        <v>sm3/d/b -&gt; SM3/D/B</v>
       </c>
       <c r="C1976" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D1976" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="E1976">
         <v>1</v>
@@ -45384,13 +45402,13 @@
       </c>
       <c r="B1977" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3d/bar -&gt; SM3D/BAR</v>
+        <v>sm3d/bar -&gt; sm3/day/bar</v>
       </c>
       <c r="C1977" t="s">
         <v>957</v>
       </c>
       <c r="D1977" t="s">
-        <v>971</v>
+        <v>954</v>
       </c>
       <c r="E1977">
         <v>1</v>
@@ -45405,13 +45423,13 @@
       </c>
       <c r="B1978" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3d/bara -&gt; sm3/day/bar</v>
+        <v>sm3d/bar -&gt; SM3D/BAR</v>
       </c>
       <c r="C1978" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D1978" t="s">
-        <v>954</v>
+        <v>971</v>
       </c>
       <c r="E1978">
         <v>1</v>
@@ -45426,13 +45444,13 @@
       </c>
       <c r="B1979" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3d/bara -&gt; SM3D/BARA</v>
+        <v>sm3d/bara -&gt; sm3/day/bar</v>
       </c>
       <c r="C1979" t="s">
         <v>958</v>
       </c>
       <c r="D1979" t="s">
-        <v>972</v>
+        <v>954</v>
       </c>
       <c r="E1979">
         <v>1</v>
@@ -45447,13 +45465,13 @@
       </c>
       <c r="B1980" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bara -&gt; sm3/day/bar</v>
+        <v>sm3d/bara -&gt; SM3D/BARA</v>
       </c>
       <c r="C1980" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D1980" t="s">
-        <v>954</v>
+        <v>972</v>
       </c>
       <c r="E1980">
         <v>1</v>
@@ -45468,13 +45486,13 @@
       </c>
       <c r="B1981" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/bara -&gt; SM3/DAY/BARA</v>
+        <v>sm3/day/bara -&gt; sm3/day/bar</v>
       </c>
       <c r="C1981" t="s">
         <v>959</v>
       </c>
       <c r="D1981" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="E1981">
         <v>1</v>
@@ -45489,13 +45507,13 @@
       </c>
       <c r="B1982" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day-bar -&gt; sm3/day/bar</v>
+        <v>sm3/day/bara -&gt; SM3/DAY/BARA</v>
       </c>
       <c r="C1982" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D1982" t="s">
-        <v>954</v>
+        <v>973</v>
       </c>
       <c r="E1982">
         <v>1</v>
@@ -45510,13 +45528,13 @@
       </c>
       <c r="B1983" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day-bar -&gt; SM3/DAY-BAR</v>
+        <v>sm3/day-bar -&gt; sm3/day/bar</v>
       </c>
       <c r="C1983" t="s">
         <v>960</v>
       </c>
       <c r="D1983" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="E1983">
         <v>1</v>
@@ -45531,13 +45549,13 @@
       </c>
       <c r="B1984" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day-bara -&gt; sm3/day/bar</v>
+        <v>sm3/day-bar -&gt; SM3/DAY-BAR</v>
       </c>
       <c r="C1984" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D1984" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
       <c r="E1984">
         <v>1</v>
@@ -45552,13 +45570,13 @@
       </c>
       <c r="B1985" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day-bara -&gt; SM3/DAY-BARA</v>
+        <v>sm3/day-bara -&gt; sm3/day/bar</v>
       </c>
       <c r="C1985" t="s">
         <v>961</v>
       </c>
       <c r="D1985" t="s">
-        <v>975</v>
+        <v>954</v>
       </c>
       <c r="E1985">
         <v>1</v>
@@ -45573,13 +45591,13 @@
       </c>
       <c r="B1986" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/kPa -&gt; sm3d/kPa</v>
+        <v>sm3/day-bara -&gt; SM3/DAY-BARA</v>
       </c>
       <c r="C1986" t="s">
-        <v>1007</v>
+        <v>961</v>
       </c>
       <c r="D1986" t="s">
-        <v>1009</v>
+        <v>975</v>
       </c>
       <c r="E1986">
         <v>1</v>
@@ -45594,13 +45612,13 @@
       </c>
       <c r="B1987" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/kPa -&gt; sm3/day-kPa</v>
+        <v>sm3/day/kPa -&gt; sm3d/kPa</v>
       </c>
       <c r="C1987" t="s">
         <v>1007</v>
       </c>
       <c r="D1987" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="E1987">
         <v>1</v>
@@ -45615,13 +45633,13 @@
       </c>
       <c r="B1988" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/kPa -&gt; sm3/d/kPa</v>
+        <v>sm3/day/kPa -&gt; sm3/day-kPa</v>
       </c>
       <c r="C1988" t="s">
         <v>1007</v>
       </c>
       <c r="D1988" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E1988">
         <v>1</v>
@@ -45636,13 +45654,13 @@
       </c>
       <c r="B1989" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day/kPa -&gt; SM3/DAY/KPA</v>
+        <v>sm3/day/kPa -&gt; sm3/d/kPa</v>
       </c>
       <c r="C1989" t="s">
         <v>1007</v>
       </c>
       <c r="D1989" t="s">
-        <v>976</v>
+        <v>1008</v>
       </c>
       <c r="E1989">
         <v>1</v>
@@ -45657,13 +45675,13 @@
       </c>
       <c r="B1990" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3d/kPa -&gt; sm3/day/kPa</v>
+        <v>sm3/day/kPa -&gt; SM3/DAY/KPA</v>
       </c>
       <c r="C1990" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D1990" t="s">
-        <v>1007</v>
+        <v>976</v>
       </c>
       <c r="E1990">
         <v>1</v>
@@ -45678,13 +45696,13 @@
       </c>
       <c r="B1991" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3d/kPa -&gt; SM3D/KPA</v>
+        <v>sm3d/kPa -&gt; sm3/day/kPa</v>
       </c>
       <c r="C1991" t="s">
         <v>1009</v>
       </c>
       <c r="D1991" t="s">
-        <v>977</v>
+        <v>1007</v>
       </c>
       <c r="E1991">
         <v>1</v>
@@ -45699,13 +45717,13 @@
       </c>
       <c r="B1992" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day-kPa -&gt; sm3/day/kPa</v>
+        <v>sm3d/kPa -&gt; SM3D/KPA</v>
       </c>
       <c r="C1992" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D1992" t="s">
-        <v>1007</v>
+        <v>977</v>
       </c>
       <c r="E1992">
         <v>1</v>
@@ -45720,13 +45738,13 @@
       </c>
       <c r="B1993" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/day-kPa -&gt; SM3/DAY-KPA</v>
+        <v>sm3/day-kPa -&gt; sm3/day/kPa</v>
       </c>
       <c r="C1993" t="s">
         <v>1006</v>
       </c>
       <c r="D1993" t="s">
-        <v>978</v>
+        <v>1007</v>
       </c>
       <c r="E1993">
         <v>1</v>
@@ -45741,13 +45759,13 @@
       </c>
       <c r="B1994" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/d/kPa -&gt; sm3/day/kPa</v>
+        <v>sm3/day-kPa -&gt; SM3/DAY-KPA</v>
       </c>
       <c r="C1994" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D1994" t="s">
-        <v>1007</v>
+        <v>978</v>
       </c>
       <c r="E1994">
         <v>1</v>
@@ -45762,13 +45780,13 @@
       </c>
       <c r="B1995" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sm3/d/kPa -&gt; SM3/D/KPA</v>
+        <v>sm3/d/kPa -&gt; sm3/day/kPa</v>
       </c>
       <c r="C1995" t="s">
         <v>1008</v>
       </c>
       <c r="D1995" t="s">
-        <v>979</v>
+        <v>1007</v>
       </c>
       <c r="E1995">
         <v>1</v>
@@ -45783,13 +45801,13 @@
       </c>
       <c r="B1996" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STB/DAY/PSI -&gt; stb/day/psi</v>
+        <v>sm3/d/kPa -&gt; SM3/D/KPA</v>
       </c>
       <c r="C1996" t="s">
-        <v>962</v>
+        <v>1008</v>
       </c>
       <c r="D1996" t="s">
-        <v>946</v>
+        <v>979</v>
       </c>
       <c r="E1996">
         <v>1</v>
@@ -45804,13 +45822,13 @@
       </c>
       <c r="B1997" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STBD/PSI -&gt; stbd/psi</v>
+        <v>STB/DAY/PSI -&gt; stb/day/psi</v>
       </c>
       <c r="C1997" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="D1997" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E1997">
         <v>1</v>
@@ -45825,13 +45843,13 @@
       </c>
       <c r="B1998" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STBD/PSIA -&gt; stbd/psia</v>
+        <v>STBD/PSI -&gt; stbd/psi</v>
       </c>
       <c r="C1998" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D1998" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E1998">
         <v>1</v>
@@ -45846,13 +45864,13 @@
       </c>
       <c r="B1999" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STB/DAY/PSIA -&gt; stb/day/psia</v>
+        <v>STBD/PSIA -&gt; stbd/psia</v>
       </c>
       <c r="C1999" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D1999" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E1999">
         <v>1</v>
@@ -45867,13 +45885,13 @@
       </c>
       <c r="B2000" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STB/DAY-PSI -&gt; stb/day-psi</v>
+        <v>STB/DAY/PSIA -&gt; stb/day/psia</v>
       </c>
       <c r="C2000" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D2000" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E2000">
         <v>1</v>
@@ -45888,13 +45906,13 @@
       </c>
       <c r="B2001" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STB/DAY-PSIA -&gt; stb/day-psia</v>
+        <v>STB/DAY-PSI -&gt; stb/day-psi</v>
       </c>
       <c r="C2001" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D2001" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E2001">
         <v>1</v>
@@ -45909,13 +45927,13 @@
       </c>
       <c r="B2002" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>STB/D/PSI -&gt; stb/d/psi</v>
+        <v>STB/DAY-PSIA -&gt; stb/day-psia</v>
       </c>
       <c r="C2002" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D2002" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E2002">
         <v>1</v>
@@ -45930,13 +45948,13 @@
       </c>
       <c r="B2003" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/BAR -&gt; sm3/day/bar</v>
+        <v>STB/D/PSI -&gt; stb/d/psi</v>
       </c>
       <c r="C2003" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D2003" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E2003">
         <v>1</v>
@@ -45951,13 +45969,13 @@
       </c>
       <c r="B2004" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/D/B -&gt; sm3/d/b</v>
+        <v>SM3/DAY/BAR -&gt; sm3/day/bar</v>
       </c>
       <c r="C2004" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D2004" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E2004">
         <v>1</v>
@@ -45972,13 +45990,13 @@
       </c>
       <c r="B2005" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3D/BAR -&gt; sm3d/bar</v>
+        <v>SM3/D/B -&gt; sm3/d/b</v>
       </c>
       <c r="C2005" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D2005" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E2005">
         <v>1</v>
@@ -45993,13 +46011,13 @@
       </c>
       <c r="B2006" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3D/BARA -&gt; sm3d/bara</v>
+        <v>SM3D/BAR -&gt; sm3d/bar</v>
       </c>
       <c r="C2006" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D2006" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E2006">
         <v>1</v>
@@ -46014,13 +46032,13 @@
       </c>
       <c r="B2007" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/BARA -&gt; sm3/day/bara</v>
+        <v>SM3D/BARA -&gt; sm3d/bara</v>
       </c>
       <c r="C2007" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D2007" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E2007">
         <v>1</v>
@@ -46035,13 +46053,13 @@
       </c>
       <c r="B2008" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY-BAR -&gt; sm3/day-bar</v>
+        <v>SM3/DAY/BARA -&gt; sm3/day/bara</v>
       </c>
       <c r="C2008" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D2008" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E2008">
         <v>1</v>
@@ -46056,13 +46074,13 @@
       </c>
       <c r="B2009" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY-BARA -&gt; sm3/day-bara</v>
+        <v>SM3/DAY-BAR -&gt; sm3/day-bar</v>
       </c>
       <c r="C2009" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D2009" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E2009">
         <v>1</v>
@@ -46077,13 +46095,13 @@
       </c>
       <c r="B2010" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/KPA -&gt; sm3/day/kPa</v>
+        <v>SM3/DAY-BARA -&gt; sm3/day-bara</v>
       </c>
       <c r="C2010" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D2010" t="s">
-        <v>1007</v>
+        <v>961</v>
       </c>
       <c r="E2010">
         <v>1</v>
@@ -46098,13 +46116,13 @@
       </c>
       <c r="B2011" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3D/KPA -&gt; sm3d/kPa</v>
+        <v>SM3/DAY/KPA -&gt; sm3/day/kPa</v>
       </c>
       <c r="C2011" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D2011" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="E2011">
         <v>1</v>
@@ -46119,13 +46137,13 @@
       </c>
       <c r="B2012" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY-KPA -&gt; sm3/day-kPa</v>
+        <v>SM3D/KPA -&gt; sm3d/kPa</v>
       </c>
       <c r="C2012" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D2012" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="E2012">
         <v>1</v>
@@ -46140,13 +46158,13 @@
       </c>
       <c r="B2013" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/D/KPA -&gt; sm3/d/kPa</v>
+        <v>SM3/DAY-KPA -&gt; sm3/day-kPa</v>
       </c>
       <c r="C2013" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D2013" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E2013">
         <v>1</v>
@@ -46161,13 +46179,13 @@
       </c>
       <c r="B2014" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sec/day -&gt; sec/d</v>
+        <v>SM3/D/KPA -&gt; sm3/d/kPa</v>
       </c>
       <c r="C2014" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D2014" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="E2014">
         <v>1</v>
@@ -46182,13 +46200,13 @@
       </c>
       <c r="B2015" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sec/day -&gt; SEC/DAY</v>
+        <v>sec/day -&gt; sec/d</v>
       </c>
       <c r="C2015" t="s">
         <v>980</v>
       </c>
       <c r="D2015" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="E2015">
         <v>1</v>
@@ -46203,13 +46221,13 @@
       </c>
       <c r="B2016" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>sec/d -&gt; sec/day</v>
+        <v>sec/day -&gt; SEC/DAY</v>
       </c>
       <c r="C2016" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D2016" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="E2016">
         <v>1</v>
@@ -46223,14 +46241,14 @@
         <v>2015</v>
       </c>
       <c r="B2017" s="2" t="str">
-        <f t="shared" ref="B2017:B2076" si="32">C2017&amp;" -&gt; " &amp;D2017</f>
-        <v>sec/d -&gt; SEC/D</v>
+        <f t="shared" si="31"/>
+        <v>sec/d -&gt; sec/day</v>
       </c>
       <c r="C2017" t="s">
         <v>981</v>
       </c>
       <c r="D2017" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E2017">
         <v>1</v>
@@ -46244,14 +46262,14 @@
         <v>2016</v>
       </c>
       <c r="B2018" s="2" t="str">
-        <f t="shared" si="32"/>
-        <v>s2 -&gt; s*s</v>
+        <f t="shared" ref="B2018:B2077" si="32">C2018&amp;" -&gt; " &amp;D2018</f>
+        <v>sec/d -&gt; SEC/D</v>
       </c>
       <c r="C2018" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D2018" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="E2018">
         <v>1</v>
@@ -46266,13 +46284,13 @@
       </c>
       <c r="B2019" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>s*s -&gt; s2</v>
+        <v>s2 -&gt; s*s</v>
       </c>
       <c r="C2019" t="s">
+        <v>982</v>
+      </c>
+      <c r="D2019" t="s">
         <v>983</v>
-      </c>
-      <c r="D2019" t="s">
-        <v>982</v>
       </c>
       <c r="E2019">
         <v>1</v>
@@ -46287,13 +46305,13 @@
       </c>
       <c r="B2020" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>s*s -&gt; S*S</v>
+        <v>s*s -&gt; s2</v>
       </c>
       <c r="C2020" t="s">
         <v>983</v>
       </c>
       <c r="D2020" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="E2020">
         <v>1</v>
@@ -46308,13 +46326,13 @@
       </c>
       <c r="B2021" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>SEC/DAY -&gt; sec/day</v>
+        <v>s*s -&gt; S*S</v>
       </c>
       <c r="C2021" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D2021" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="E2021">
         <v>1</v>
@@ -46329,13 +46347,13 @@
       </c>
       <c r="B2022" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>SEC/D -&gt; sec/d</v>
+        <v>SEC/DAY -&gt; sec/day</v>
       </c>
       <c r="C2022" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D2022" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E2022">
         <v>1</v>
@@ -46350,13 +46368,13 @@
       </c>
       <c r="B2023" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fraction -&gt; ratio</v>
+        <v>SEC/D -&gt; sec/d</v>
       </c>
       <c r="C2023" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D2023" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="E2023">
         <v>1</v>
@@ -46371,13 +46389,13 @@
       </c>
       <c r="B2024" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fraction -&gt; dimensionless</v>
+        <v>fraction -&gt; ratio</v>
       </c>
       <c r="C2024" t="s">
         <v>987</v>
       </c>
       <c r="D2024" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E2024">
         <v>1</v>
@@ -46392,13 +46410,13 @@
       </c>
       <c r="B2025" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fraction -&gt; unitless</v>
+        <v>fraction -&gt; dimensionless</v>
       </c>
       <c r="C2025" t="s">
         <v>987</v>
       </c>
       <c r="D2025" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E2025">
         <v>1</v>
@@ -46413,13 +46431,13 @@
       </c>
       <c r="B2026" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fraction -&gt; FRACTION</v>
+        <v>fraction -&gt; unitless</v>
       </c>
       <c r="C2026" t="s">
         <v>987</v>
       </c>
       <c r="D2026" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E2026">
         <v>1</v>
@@ -46434,19 +46452,19 @@
       </c>
       <c r="B2027" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fraction -&gt; percentage</v>
+        <v>fraction -&gt; FRACTION</v>
       </c>
       <c r="C2027" t="s">
         <v>987</v>
       </c>
       <c r="D2027" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="E2027">
         <v>1</v>
       </c>
       <c r="F2027">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2028" spans="1:6" x14ac:dyDescent="0.3">
@@ -46455,19 +46473,19 @@
       </c>
       <c r="B2028" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>percentage -&gt; fraction</v>
+        <v>fraction -&gt; percentage</v>
       </c>
       <c r="C2028" t="s">
+        <v>987</v>
+      </c>
+      <c r="D2028" t="s">
         <v>995</v>
       </c>
-      <c r="D2028" t="s">
-        <v>987</v>
-      </c>
       <c r="E2028">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="F2028">
-        <v>0.85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2029" spans="1:6" x14ac:dyDescent="0.3">
@@ -46476,19 +46494,19 @@
       </c>
       <c r="B2029" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>ratio -&gt; fraction</v>
+        <v>percentage -&gt; fraction</v>
       </c>
       <c r="C2029" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="D2029" t="s">
         <v>987</v>
       </c>
       <c r="E2029">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F2029">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="2030" spans="1:6" x14ac:dyDescent="0.3">
@@ -46497,13 +46515,13 @@
       </c>
       <c r="B2030" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>ratio -&gt; RATIO</v>
+        <v>ratio -&gt; fraction</v>
       </c>
       <c r="C2030" t="s">
         <v>988</v>
       </c>
       <c r="D2030" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="E2030">
         <v>1</v>
@@ -46518,13 +46536,13 @@
       </c>
       <c r="B2031" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>dimensionless -&gt; fraction</v>
+        <v>ratio -&gt; RATIO</v>
       </c>
       <c r="C2031" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D2031" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="E2031">
         <v>1</v>
@@ -46539,13 +46557,13 @@
       </c>
       <c r="B2032" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>dimensionless -&gt; DIMENSIONLESS</v>
+        <v>dimensionless -&gt; fraction</v>
       </c>
       <c r="C2032" t="s">
         <v>989</v>
       </c>
       <c r="D2032" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="E2032">
         <v>1</v>
@@ -46560,13 +46578,13 @@
       </c>
       <c r="B2033" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>unitless -&gt; fraction</v>
+        <v>dimensionless -&gt; DIMENSIONLESS</v>
       </c>
       <c r="C2033" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D2033" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="E2033">
         <v>1</v>
@@ -46581,13 +46599,13 @@
       </c>
       <c r="B2034" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>unitless -&gt; UNITLESS</v>
+        <v>unitless -&gt; fraction</v>
       </c>
       <c r="C2034" t="s">
         <v>990</v>
       </c>
       <c r="D2034" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="E2034">
         <v>1</v>
@@ -46602,13 +46620,13 @@
       </c>
       <c r="B2035" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>FRACTION -&gt; fraction</v>
+        <v>unitless -&gt; UNITLESS</v>
       </c>
       <c r="C2035" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D2035" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="E2035">
         <v>1</v>
@@ -46623,13 +46641,13 @@
       </c>
       <c r="B2036" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>RATIO -&gt; ratio</v>
+        <v>FRACTION -&gt; fraction</v>
       </c>
       <c r="C2036" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D2036" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E2036">
         <v>1</v>
@@ -46644,13 +46662,13 @@
       </c>
       <c r="B2037" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>DIMENSIONLESS -&gt; dimensionless</v>
+        <v>RATIO -&gt; ratio</v>
       </c>
       <c r="C2037" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D2037" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E2037">
         <v>1</v>
@@ -46665,13 +46683,13 @@
       </c>
       <c r="B2038" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>UNITLESS -&gt; unitless</v>
+        <v>DIMENSIONLESS -&gt; dimensionless</v>
       </c>
       <c r="C2038" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D2038" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E2038">
         <v>1</v>
@@ -46686,13 +46704,13 @@
       </c>
       <c r="B2039" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>percentage -&gt; %</v>
+        <v>UNITLESS -&gt; unitless</v>
       </c>
       <c r="C2039" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D2039" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="E2039">
         <v>1</v>
@@ -46707,13 +46725,13 @@
       </c>
       <c r="B2040" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>% -&gt; percentage</v>
+        <v>percentage -&gt; %</v>
       </c>
       <c r="C2040" t="s">
+        <v>995</v>
+      </c>
+      <c r="D2040" t="s">
         <v>996</v>
-      </c>
-      <c r="D2040" t="s">
-        <v>995</v>
       </c>
       <c r="E2040">
         <v>1</v>
@@ -46728,13 +46746,13 @@
       </c>
       <c r="B2041" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>date -&gt; dates</v>
+        <v>% -&gt; percentage</v>
       </c>
       <c r="C2041" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D2041" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="E2041">
         <v>1</v>
@@ -46749,13 +46767,13 @@
       </c>
       <c r="B2042" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>date -&gt; DATES</v>
+        <v>date -&gt; dates</v>
       </c>
       <c r="C2042" t="s">
         <v>997</v>
       </c>
       <c r="D2042" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E2042">
         <v>1</v>
@@ -46770,13 +46788,13 @@
       </c>
       <c r="B2043" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>date -&gt; DATE</v>
+        <v>date -&gt; DATES</v>
       </c>
       <c r="C2043" t="s">
         <v>997</v>
       </c>
       <c r="D2043" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E2043">
         <v>1</v>
@@ -46791,13 +46809,13 @@
       </c>
       <c r="B2044" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>dates -&gt; date</v>
+        <v>date -&gt; DATE</v>
       </c>
       <c r="C2044" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D2044" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E2044">
         <v>1</v>
@@ -46812,10 +46830,10 @@
       </c>
       <c r="B2045" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>DATES -&gt; date</v>
+        <v>dates -&gt; date</v>
       </c>
       <c r="C2045" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D2045" t="s">
         <v>997</v>
@@ -46833,10 +46851,10 @@
       </c>
       <c r="B2046" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>DATE -&gt; date</v>
+        <v>DATES -&gt; date</v>
       </c>
       <c r="C2046" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D2046" t="s">
         <v>997</v>
@@ -46854,13 +46872,13 @@
       </c>
       <c r="B2047" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>W -&gt; Watt</v>
+        <v>DATE -&gt; date</v>
       </c>
       <c r="C2047" t="s">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="D2047" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="E2047">
         <v>1</v>
@@ -46875,13 +46893,13 @@
       </c>
       <c r="B2048" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>W -&gt; W</v>
+        <v>W -&gt; Watt</v>
       </c>
       <c r="C2048" t="s">
         <v>70</v>
       </c>
       <c r="D2048" t="s">
-        <v>70</v>
+        <v>1010</v>
       </c>
       <c r="E2048">
         <v>1</v>
@@ -46896,13 +46914,13 @@
       </c>
       <c r="B2049" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce -&gt; ozUS</v>
+        <v>W -&gt; W</v>
       </c>
       <c r="C2049" t="s">
-        <v>1107</v>
+        <v>70</v>
       </c>
       <c r="D2049" t="s">
-        <v>1011</v>
+        <v>70</v>
       </c>
       <c r="E2049">
         <v>1</v>
@@ -46917,19 +46935,19 @@
       </c>
       <c r="B2050" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce -&gt; gallonUS</v>
+        <v>fluid ounce -&gt; ozUS</v>
       </c>
       <c r="C2050" t="s">
         <v>1107</v>
       </c>
       <c r="D2050" t="s">
-        <v>357</v>
+        <v>1011</v>
       </c>
       <c r="E2050">
         <v>1</v>
       </c>
       <c r="F2050">
-        <v>7.8125E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2051" spans="1:6" x14ac:dyDescent="0.3">
@@ -46938,19 +46956,19 @@
       </c>
       <c r="B2051" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>ozUS -&gt; fluid ounce</v>
+        <v>fluid ounce -&gt; gallonUS</v>
       </c>
       <c r="C2051" t="s">
-        <v>1011</v>
+        <v>1107</v>
       </c>
       <c r="D2051" t="s">
-        <v>1107</v>
+        <v>357</v>
       </c>
       <c r="E2051">
         <v>1</v>
       </c>
       <c r="F2051">
-        <v>1</v>
+        <v>7.8125E-3</v>
       </c>
     </row>
     <row r="2052" spans="1:6" x14ac:dyDescent="0.3">
@@ -46959,13 +46977,13 @@
       </c>
       <c r="B2052" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gill -&gt; gillUS</v>
+        <v>ozUS -&gt; fluid ounce</v>
       </c>
       <c r="C2052" t="s">
-        <v>345</v>
+        <v>1011</v>
       </c>
       <c r="D2052" t="s">
-        <v>1012</v>
+        <v>1107</v>
       </c>
       <c r="E2052">
         <v>1</v>
@@ -46980,13 +46998,13 @@
       </c>
       <c r="B2053" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gill -&gt; giUS</v>
+        <v>gill -&gt; gillUS</v>
       </c>
       <c r="C2053" t="s">
         <v>345</v>
       </c>
       <c r="D2053" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E2053">
         <v>1</v>
@@ -47001,13 +47019,13 @@
       </c>
       <c r="B2054" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gillUS -&gt; gill</v>
+        <v>gill -&gt; giUS</v>
       </c>
       <c r="C2054" t="s">
-        <v>1012</v>
+        <v>345</v>
       </c>
       <c r="D2054" t="s">
-        <v>345</v>
+        <v>1013</v>
       </c>
       <c r="E2054">
         <v>1</v>
@@ -47022,10 +47040,10 @@
       </c>
       <c r="B2055" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>giUS -&gt; gill</v>
+        <v>gillUS -&gt; gill</v>
       </c>
       <c r="C2055" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D2055" t="s">
         <v>345</v>
@@ -47043,13 +47061,13 @@
       </c>
       <c r="B2056" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>pint -&gt; pintUS</v>
+        <v>giUS -&gt; gill</v>
       </c>
       <c r="C2056" t="s">
-        <v>347</v>
+        <v>1013</v>
       </c>
       <c r="D2056" t="s">
-        <v>1014</v>
+        <v>345</v>
       </c>
       <c r="E2056">
         <v>1</v>
@@ -47064,13 +47082,13 @@
       </c>
       <c r="B2057" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>pint -&gt; ptUS</v>
+        <v>pint -&gt; pintUS</v>
       </c>
       <c r="C2057" t="s">
         <v>347</v>
       </c>
       <c r="D2057" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E2057">
         <v>1</v>
@@ -47085,13 +47103,13 @@
       </c>
       <c r="B2058" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>pintUS -&gt; pint</v>
+        <v>pint -&gt; ptUS</v>
       </c>
       <c r="C2058" t="s">
-        <v>1014</v>
+        <v>347</v>
       </c>
       <c r="D2058" t="s">
-        <v>347</v>
+        <v>1015</v>
       </c>
       <c r="E2058">
         <v>1</v>
@@ -47106,10 +47124,10 @@
       </c>
       <c r="B2059" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>ptUS -&gt; pint</v>
+        <v>pintUS -&gt; pint</v>
       </c>
       <c r="C2059" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D2059" t="s">
         <v>347</v>
@@ -47127,13 +47145,13 @@
       </c>
       <c r="B2060" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>quart -&gt; quartUS</v>
+        <v>ptUS -&gt; pint</v>
       </c>
       <c r="C2060" t="s">
-        <v>349</v>
+        <v>1015</v>
       </c>
       <c r="D2060" t="s">
-        <v>1016</v>
+        <v>347</v>
       </c>
       <c r="E2060">
         <v>1</v>
@@ -47148,19 +47166,19 @@
       </c>
       <c r="B2061" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>quart -&gt; gallonUS</v>
+        <v>quart -&gt; quartUS</v>
       </c>
       <c r="C2061" t="s">
         <v>349</v>
       </c>
       <c r="D2061" t="s">
-        <v>357</v>
+        <v>1016</v>
       </c>
       <c r="E2061">
         <v>1</v>
       </c>
       <c r="F2061">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2062" spans="1:6" x14ac:dyDescent="0.3">
@@ -47169,19 +47187,19 @@
       </c>
       <c r="B2062" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>quartUS -&gt; quart</v>
+        <v>quart -&gt; gallonUS</v>
       </c>
       <c r="C2062" t="s">
-        <v>1016</v>
+        <v>349</v>
       </c>
       <c r="D2062" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E2062">
         <v>1</v>
       </c>
       <c r="F2062">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="2063" spans="1:6" x14ac:dyDescent="0.3">
@@ -47190,10 +47208,10 @@
       </c>
       <c r="B2063" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>qtUS -&gt; quart</v>
+        <v>quartUS -&gt; quart</v>
       </c>
       <c r="C2063" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D2063" t="s">
         <v>349</v>
@@ -47211,19 +47229,19 @@
       </c>
       <c r="B2064" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gallonUS -&gt; fluid ounce</v>
+        <v>qtUS -&gt; quart</v>
       </c>
       <c r="C2064" t="s">
-        <v>357</v>
+        <v>1017</v>
       </c>
       <c r="D2064" t="s">
-        <v>1107</v>
+        <v>349</v>
       </c>
       <c r="E2064">
         <v>1</v>
       </c>
       <c r="F2064">
-        <v>128</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2065" spans="1:6" x14ac:dyDescent="0.3">
@@ -47232,19 +47250,19 @@
       </c>
       <c r="B2065" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gallonUS -&gt; quart</v>
+        <v>gallonUS -&gt; fluid ounce</v>
       </c>
       <c r="C2065" t="s">
         <v>357</v>
       </c>
       <c r="D2065" t="s">
-        <v>349</v>
+        <v>1107</v>
       </c>
       <c r="E2065">
         <v>1</v>
       </c>
       <c r="F2065">
-        <v>4</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2066" spans="1:6" x14ac:dyDescent="0.3">
@@ -47253,19 +47271,19 @@
       </c>
       <c r="B2066" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gallonUK -&gt; imperial gallon</v>
+        <v>gallonUS -&gt; quart</v>
       </c>
       <c r="C2066" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D2066" t="s">
-        <v>1018</v>
+        <v>349</v>
       </c>
       <c r="E2066">
         <v>1</v>
       </c>
       <c r="F2066">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2067" spans="1:6" x14ac:dyDescent="0.3">
@@ -47274,19 +47292,19 @@
       </c>
       <c r="B2067" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gallonUK -&gt; quartUK</v>
+        <v>gallonUK -&gt; imperial gallon</v>
       </c>
       <c r="C2067" t="s">
         <v>351</v>
       </c>
       <c r="D2067" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E2067">
         <v>1</v>
       </c>
       <c r="F2067">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2068" spans="1:6" x14ac:dyDescent="0.3">
@@ -47295,19 +47313,19 @@
       </c>
       <c r="B2068" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gallonUK -&gt; fluid ounce UK</v>
+        <v>gallonUK -&gt; quartUK</v>
       </c>
       <c r="C2068" t="s">
         <v>351</v>
       </c>
       <c r="D2068" t="s">
-        <v>1109</v>
+        <v>1019</v>
       </c>
       <c r="E2068">
         <v>1</v>
       </c>
       <c r="F2068">
-        <v>160</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2069" spans="1:6" x14ac:dyDescent="0.3">
@@ -47316,19 +47334,19 @@
       </c>
       <c r="B2069" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>gallonUK -&gt; litre</v>
+        <v>gallonUK -&gt; fluid ounce UK</v>
       </c>
       <c r="C2069" t="s">
         <v>351</v>
       </c>
       <c r="D2069" t="s">
-        <v>380</v>
+        <v>1109</v>
       </c>
       <c r="E2069">
         <v>1</v>
       </c>
       <c r="F2069">
-        <v>4.5460000000000003</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2070" spans="1:6" x14ac:dyDescent="0.3">
@@ -47337,19 +47355,19 @@
       </c>
       <c r="B2070" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>imperial gallon -&gt; gallonUK</v>
+        <v>gallonUK -&gt; litre</v>
       </c>
       <c r="C2070" t="s">
-        <v>1018</v>
+        <v>351</v>
       </c>
       <c r="D2070" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="E2070">
         <v>1</v>
       </c>
       <c r="F2070">
-        <v>1</v>
+        <v>4.5460000000000003</v>
       </c>
     </row>
     <row r="2071" spans="1:6" x14ac:dyDescent="0.3">
@@ -47358,13 +47376,13 @@
       </c>
       <c r="B2071" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>imperial gallon -&gt; IMPERIAL GALLON</v>
+        <v>imperial gallon -&gt; gallonUK</v>
       </c>
       <c r="C2071" t="s">
         <v>1018</v>
       </c>
       <c r="D2071" t="s">
-        <v>1020</v>
+        <v>351</v>
       </c>
       <c r="E2071">
         <v>1</v>
@@ -47379,13 +47397,13 @@
       </c>
       <c r="B2072" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce UK -&gt; fl oz UK</v>
+        <v>imperial gallon -&gt; IMPERIAL GALLON</v>
       </c>
       <c r="C2072" t="s">
-        <v>1109</v>
+        <v>1018</v>
       </c>
       <c r="D2072" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E2072">
         <v>1</v>
@@ -47400,13 +47418,13 @@
       </c>
       <c r="B2073" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce UK -&gt; ozUK</v>
+        <v>fluid ounce UK -&gt; fl oz UK</v>
       </c>
       <c r="C2073" t="s">
         <v>1109</v>
       </c>
       <c r="D2073" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E2073">
         <v>1</v>
@@ -47421,13 +47439,13 @@
       </c>
       <c r="B2074" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce UK -&gt; ounceUK</v>
+        <v>fluid ounce UK -&gt; ozUK</v>
       </c>
       <c r="C2074" t="s">
         <v>1109</v>
       </c>
       <c r="D2074" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E2074">
         <v>1</v>
@@ -47442,13 +47460,13 @@
       </c>
       <c r="B2075" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce UK -&gt; fluid ounce UKs</v>
+        <v>fluid ounce UK -&gt; ounceUK</v>
       </c>
       <c r="C2075" t="s">
         <v>1109</v>
       </c>
       <c r="D2075" t="s">
-        <v>1110</v>
+        <v>1023</v>
       </c>
       <c r="E2075">
         <v>1</v>
@@ -47463,13 +47481,13 @@
       </c>
       <c r="B2076" s="2" t="str">
         <f t="shared" si="32"/>
-        <v>fluid ounce UK -&gt; FLUID OUNCE UKS</v>
+        <v>fluid ounce UK -&gt; fluid ounce UKs</v>
       </c>
       <c r="C2076" t="s">
         <v>1109</v>
       </c>
       <c r="D2076" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="E2076">
         <v>1</v>
@@ -47483,14 +47501,14 @@
         <v>2075</v>
       </c>
       <c r="B2077" s="2" t="str">
-        <f t="shared" ref="B2077:B2140" si="33">C2077&amp;" -&gt; " &amp;D2077</f>
-        <v>fluid ounce UK -&gt; FLUID OUNCE UK</v>
+        <f t="shared" si="32"/>
+        <v>fluid ounce UK -&gt; FLUID OUNCE UKS</v>
       </c>
       <c r="C2077" t="s">
         <v>1109</v>
       </c>
       <c r="D2077" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E2077">
         <v>1</v>
@@ -47504,20 +47522,20 @@
         <v>2076</v>
       </c>
       <c r="B2078" s="2" t="str">
-        <f t="shared" si="33"/>
-        <v>fluid ounce UK -&gt; gallonUK</v>
+        <f t="shared" ref="B2078:B2141" si="33">C2078&amp;" -&gt; " &amp;D2078</f>
+        <v>fluid ounce UK -&gt; FLUID OUNCE UK</v>
       </c>
       <c r="C2078" t="s">
         <v>1109</v>
       </c>
       <c r="D2078" t="s">
-        <v>351</v>
+        <v>1115</v>
       </c>
       <c r="E2078">
         <v>1</v>
       </c>
       <c r="F2078">
-        <v>6.2500000000000003E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2079" spans="1:6" x14ac:dyDescent="0.3">
@@ -47526,19 +47544,19 @@
       </c>
       <c r="B2079" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>fluid ounce UK -&gt; gillUK</v>
+        <v>fluid ounce UK -&gt; gallonUK</v>
       </c>
       <c r="C2079" t="s">
         <v>1109</v>
       </c>
       <c r="D2079" t="s">
-        <v>1024</v>
+        <v>351</v>
       </c>
       <c r="E2079">
         <v>1</v>
       </c>
       <c r="F2079">
-        <v>0.25</v>
+        <v>6.2500000000000003E-3</v>
       </c>
     </row>
     <row r="2080" spans="1:6" x14ac:dyDescent="0.3">
@@ -47547,19 +47565,19 @@
       </c>
       <c r="B2080" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>fl oz UK -&gt; fluid ounce UK</v>
+        <v>fluid ounce UK -&gt; gillUK</v>
       </c>
       <c r="C2080" t="s">
-        <v>1021</v>
+        <v>1109</v>
       </c>
       <c r="D2080" t="s">
-        <v>1109</v>
+        <v>1024</v>
       </c>
       <c r="E2080">
         <v>1</v>
       </c>
       <c r="F2080">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="2081" spans="1:6" x14ac:dyDescent="0.3">
@@ -47568,10 +47586,10 @@
       </c>
       <c r="B2081" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>ozUK -&gt; fluid ounce UK</v>
+        <v>fl oz UK -&gt; fluid ounce UK</v>
       </c>
       <c r="C2081" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D2081" t="s">
         <v>1109</v>
@@ -47589,10 +47607,10 @@
       </c>
       <c r="B2082" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>ounceUK -&gt; fluid ounce UK</v>
+        <v>ozUK -&gt; fluid ounce UK</v>
       </c>
       <c r="C2082" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D2082" t="s">
         <v>1109</v>
@@ -47610,13 +47628,13 @@
       </c>
       <c r="B2083" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUK -&gt; giUK</v>
+        <v>ounceUK -&gt; fluid ounce UK</v>
       </c>
       <c r="C2083" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D2083" t="s">
-        <v>1025</v>
+        <v>1109</v>
       </c>
       <c r="E2083">
         <v>1</v>
@@ -47631,13 +47649,13 @@
       </c>
       <c r="B2084" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUK -&gt; gillUKs</v>
+        <v>gillUK -&gt; giUK</v>
       </c>
       <c r="C2084" t="s">
         <v>1024</v>
       </c>
       <c r="D2084" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E2084">
         <v>1</v>
@@ -47652,13 +47670,13 @@
       </c>
       <c r="B2085" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUK -&gt; GILLUKS</v>
+        <v>gillUK -&gt; gillUKs</v>
       </c>
       <c r="C2085" t="s">
         <v>1024</v>
       </c>
       <c r="D2085" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E2085">
         <v>1</v>
@@ -47673,13 +47691,13 @@
       </c>
       <c r="B2086" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUK -&gt; GILLUK</v>
+        <v>gillUK -&gt; GILLUKS</v>
       </c>
       <c r="C2086" t="s">
         <v>1024</v>
       </c>
       <c r="D2086" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E2086">
         <v>1</v>
@@ -47694,19 +47712,19 @@
       </c>
       <c r="B2087" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUK -&gt; fluid ounce UK</v>
+        <v>gillUK -&gt; GILLUK</v>
       </c>
       <c r="C2087" t="s">
         <v>1024</v>
       </c>
       <c r="D2087" t="s">
-        <v>1109</v>
+        <v>1028</v>
       </c>
       <c r="E2087">
         <v>1</v>
       </c>
       <c r="F2087">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2088" spans="1:6" x14ac:dyDescent="0.3">
@@ -47715,19 +47733,19 @@
       </c>
       <c r="B2088" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUK -&gt; pintUK</v>
+        <v>gillUK -&gt; fluid ounce UK</v>
       </c>
       <c r="C2088" t="s">
         <v>1024</v>
       </c>
       <c r="D2088" t="s">
-        <v>1029</v>
+        <v>1109</v>
       </c>
       <c r="E2088">
         <v>1</v>
       </c>
       <c r="F2088">
-        <v>0.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2089" spans="1:6" x14ac:dyDescent="0.3">
@@ -47736,19 +47754,19 @@
       </c>
       <c r="B2089" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>giUK -&gt; gillUK</v>
+        <v>gillUK -&gt; pintUK</v>
       </c>
       <c r="C2089" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="D2089" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="E2089">
         <v>1</v>
       </c>
       <c r="F2089">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="2090" spans="1:6" x14ac:dyDescent="0.3">
@@ -47757,13 +47775,13 @@
       </c>
       <c r="B2090" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUK -&gt; ptUK</v>
+        <v>giUK -&gt; gillUK</v>
       </c>
       <c r="C2090" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="D2090" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="E2090">
         <v>1</v>
@@ -47778,13 +47796,13 @@
       </c>
       <c r="B2091" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUK -&gt; pintUKs</v>
+        <v>pintUK -&gt; ptUK</v>
       </c>
       <c r="C2091" t="s">
         <v>1029</v>
       </c>
       <c r="D2091" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E2091">
         <v>1</v>
@@ -47799,13 +47817,13 @@
       </c>
       <c r="B2092" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUK -&gt; PINTUKS</v>
+        <v>pintUK -&gt; pintUKs</v>
       </c>
       <c r="C2092" t="s">
         <v>1029</v>
       </c>
       <c r="D2092" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E2092">
         <v>1</v>
@@ -47820,13 +47838,13 @@
       </c>
       <c r="B2093" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUK -&gt; PINTUK</v>
+        <v>pintUK -&gt; PINTUKS</v>
       </c>
       <c r="C2093" t="s">
         <v>1029</v>
       </c>
       <c r="D2093" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E2093">
         <v>1</v>
@@ -47841,19 +47859,19 @@
       </c>
       <c r="B2094" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUK -&gt; gillUK</v>
+        <v>pintUK -&gt; PINTUK</v>
       </c>
       <c r="C2094" t="s">
         <v>1029</v>
       </c>
       <c r="D2094" t="s">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="E2094">
         <v>1</v>
       </c>
       <c r="F2094">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2095" spans="1:6" x14ac:dyDescent="0.3">
@@ -47862,19 +47880,19 @@
       </c>
       <c r="B2095" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUK -&gt; quartUK</v>
+        <v>pintUK -&gt; gillUK</v>
       </c>
       <c r="C2095" t="s">
         <v>1029</v>
       </c>
       <c r="D2095" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
       <c r="E2095">
         <v>1</v>
       </c>
       <c r="F2095">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2096" spans="1:6" x14ac:dyDescent="0.3">
@@ -47883,19 +47901,19 @@
       </c>
       <c r="B2096" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>ptUK -&gt; pintUK</v>
+        <v>pintUK -&gt; quartUK</v>
       </c>
       <c r="C2096" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D2096" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
       <c r="E2096">
         <v>1</v>
       </c>
       <c r="F2096">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="2097" spans="1:6" x14ac:dyDescent="0.3">
@@ -47904,13 +47922,13 @@
       </c>
       <c r="B2097" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUK -&gt; qtUK</v>
+        <v>ptUK -&gt; pintUK</v>
       </c>
       <c r="C2097" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="D2097" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="E2097">
         <v>1</v>
@@ -47925,13 +47943,13 @@
       </c>
       <c r="B2098" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUK -&gt; quartUKs</v>
+        <v>quartUK -&gt; qtUK</v>
       </c>
       <c r="C2098" t="s">
         <v>1019</v>
       </c>
       <c r="D2098" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E2098">
         <v>1</v>
@@ -47946,13 +47964,13 @@
       </c>
       <c r="B2099" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUK -&gt; QUARTUKS</v>
+        <v>quartUK -&gt; quartUKs</v>
       </c>
       <c r="C2099" t="s">
         <v>1019</v>
       </c>
       <c r="D2099" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E2099">
         <v>1</v>
@@ -47967,13 +47985,13 @@
       </c>
       <c r="B2100" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUK -&gt; QUARTUK</v>
+        <v>quartUK -&gt; QUARTUKS</v>
       </c>
       <c r="C2100" t="s">
         <v>1019</v>
       </c>
       <c r="D2100" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E2100">
         <v>1</v>
@@ -47988,19 +48006,19 @@
       </c>
       <c r="B2101" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUK -&gt; pintUK</v>
+        <v>quartUK -&gt; QUARTUK</v>
       </c>
       <c r="C2101" t="s">
         <v>1019</v>
       </c>
       <c r="D2101" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="E2101">
         <v>1</v>
       </c>
       <c r="F2101">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2102" spans="1:6" x14ac:dyDescent="0.3">
@@ -48009,19 +48027,19 @@
       </c>
       <c r="B2102" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUK -&gt; gallonUK</v>
+        <v>quartUK -&gt; pintUK</v>
       </c>
       <c r="C2102" t="s">
         <v>1019</v>
       </c>
       <c r="D2102" t="s">
-        <v>351</v>
+        <v>1029</v>
       </c>
       <c r="E2102">
         <v>1</v>
       </c>
       <c r="F2102">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2103" spans="1:6" x14ac:dyDescent="0.3">
@@ -48030,19 +48048,19 @@
       </c>
       <c r="B2103" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>qtUK -&gt; quartUK</v>
+        <v>quartUK -&gt; gallonUK</v>
       </c>
       <c r="C2103" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="D2103" t="s">
-        <v>1019</v>
+        <v>351</v>
       </c>
       <c r="E2103">
         <v>1</v>
       </c>
       <c r="F2103">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="2104" spans="1:6" x14ac:dyDescent="0.3">
@@ -48051,13 +48069,13 @@
       </c>
       <c r="B2104" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>fluid ounce UKs -&gt; fluid ounce UK</v>
+        <v>qtUK -&gt; quartUK</v>
       </c>
       <c r="C2104" t="s">
-        <v>1110</v>
+        <v>1034</v>
       </c>
       <c r="D2104" t="s">
-        <v>1109</v>
+        <v>1019</v>
       </c>
       <c r="E2104">
         <v>1</v>
@@ -48072,13 +48090,13 @@
       </c>
       <c r="B2105" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>gillUKs -&gt; gillUK</v>
+        <v>fluid ounce UKs -&gt; fluid ounce UK</v>
       </c>
       <c r="C2105" t="s">
-        <v>1026</v>
+        <v>1110</v>
       </c>
       <c r="D2105" t="s">
-        <v>1024</v>
+        <v>1109</v>
       </c>
       <c r="E2105">
         <v>1</v>
@@ -48093,13 +48111,13 @@
       </c>
       <c r="B2106" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>pintUKs -&gt; pintUK</v>
+        <v>gillUKs -&gt; gillUK</v>
       </c>
       <c r="C2106" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="D2106" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E2106">
         <v>1</v>
@@ -48114,13 +48132,13 @@
       </c>
       <c r="B2107" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>quartUKs -&gt; quartUK</v>
+        <v>pintUKs -&gt; pintUK</v>
       </c>
       <c r="C2107" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="D2107" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="E2107">
         <v>1</v>
@@ -48135,13 +48153,13 @@
       </c>
       <c r="B2108" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>FLUID OUNCE UKS -&gt; fluid ounce UK</v>
+        <v>quartUKs -&gt; quartUK</v>
       </c>
       <c r="C2108" t="s">
-        <v>1114</v>
+        <v>1035</v>
       </c>
       <c r="D2108" t="s">
-        <v>1109</v>
+        <v>1019</v>
       </c>
       <c r="E2108">
         <v>1</v>
@@ -48156,13 +48174,13 @@
       </c>
       <c r="B2109" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>GILLUKS -&gt; gillUK</v>
+        <v>FLUID OUNCE UKS -&gt; fluid ounce UK</v>
       </c>
       <c r="C2109" t="s">
-        <v>1027</v>
+        <v>1114</v>
       </c>
       <c r="D2109" t="s">
-        <v>1024</v>
+        <v>1109</v>
       </c>
       <c r="E2109">
         <v>1</v>
@@ -48177,13 +48195,13 @@
       </c>
       <c r="B2110" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>PINTUKS -&gt; pintUK</v>
+        <v>GILLUKS -&gt; gillUK</v>
       </c>
       <c r="C2110" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="D2110" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E2110">
         <v>1</v>
@@ -48198,13 +48216,13 @@
       </c>
       <c r="B2111" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>QUARTUKS -&gt; quartUK</v>
+        <v>PINTUKS -&gt; pintUK</v>
       </c>
       <c r="C2111" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D2111" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="E2111">
         <v>1</v>
@@ -48219,13 +48237,13 @@
       </c>
       <c r="B2112" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>IMPERIAL GALLON -&gt; imperial gallon</v>
+        <v>QUARTUKS -&gt; quartUK</v>
       </c>
       <c r="C2112" t="s">
-        <v>1020</v>
+        <v>1036</v>
       </c>
       <c r="D2112" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E2112">
         <v>1</v>
@@ -48240,13 +48258,13 @@
       </c>
       <c r="B2113" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>FLUID OUNCE UK -&gt; fluid ounce UK</v>
+        <v>IMPERIAL GALLON -&gt; imperial gallon</v>
       </c>
       <c r="C2113" t="s">
-        <v>1115</v>
+        <v>1020</v>
       </c>
       <c r="D2113" t="s">
-        <v>1109</v>
+        <v>1018</v>
       </c>
       <c r="E2113">
         <v>1</v>
@@ -48261,13 +48279,13 @@
       </c>
       <c r="B2114" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>GILLUK -&gt; gillUK</v>
+        <v>FLUID OUNCE UK -&gt; fluid ounce UK</v>
       </c>
       <c r="C2114" t="s">
-        <v>1028</v>
+        <v>1115</v>
       </c>
       <c r="D2114" t="s">
-        <v>1024</v>
+        <v>1109</v>
       </c>
       <c r="E2114">
         <v>1</v>
@@ -48282,13 +48300,13 @@
       </c>
       <c r="B2115" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>PINTUK -&gt; pintUK</v>
+        <v>GILLUK -&gt; gillUK</v>
       </c>
       <c r="C2115" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="D2115" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E2115">
         <v>1</v>
@@ -48303,13 +48321,13 @@
       </c>
       <c r="B2116" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>QUARTUK -&gt; quartUK</v>
+        <v>PINTUK -&gt; pintUK</v>
       </c>
       <c r="C2116" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="D2116" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="E2116">
         <v>1</v>
@@ -48324,19 +48342,19 @@
       </c>
       <c r="B2117" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>litre -&gt; gallonUK</v>
+        <v>QUARTUK -&gt; quartUK</v>
       </c>
       <c r="C2117" t="s">
-        <v>380</v>
+        <v>1037</v>
       </c>
       <c r="D2117" t="s">
-        <v>351</v>
+        <v>1019</v>
       </c>
       <c r="E2117">
         <v>1</v>
       </c>
       <c r="F2117">
-        <v>0.21997360316761991</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2118" spans="1:6" x14ac:dyDescent="0.3">
@@ -48345,19 +48363,19 @@
       </c>
       <c r="B2118" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Pa -&gt; KPa</v>
+        <v>litre -&gt; gallonUK</v>
       </c>
       <c r="C2118" t="s">
-        <v>567</v>
+        <v>380</v>
       </c>
       <c r="D2118" t="s">
-        <v>570</v>
+        <v>351</v>
       </c>
       <c r="E2118">
         <v>1</v>
       </c>
       <c r="F2118">
-        <v>1E-3</v>
+        <v>0.21997360316761991</v>
       </c>
     </row>
     <row r="2119" spans="1:6" x14ac:dyDescent="0.3">
@@ -48366,10 +48384,10 @@
       </c>
       <c r="B2119" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>kPa -&gt; KPa</v>
+        <v>Pa -&gt; KPa</v>
       </c>
       <c r="C2119" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D2119" t="s">
         <v>570</v>
@@ -48378,7 +48396,7 @@
         <v>1</v>
       </c>
       <c r="F2119">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="2120" spans="1:6" x14ac:dyDescent="0.3">
@@ -48387,13 +48405,13 @@
       </c>
       <c r="B2120" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>KPa -&gt; kPa</v>
+        <v>kPa -&gt; KPa</v>
       </c>
       <c r="C2120" t="s">
+        <v>569</v>
+      </c>
+      <c r="D2120" t="s">
         <v>570</v>
-      </c>
-      <c r="D2120" t="s">
-        <v>569</v>
       </c>
       <c r="E2120">
         <v>1</v>
@@ -48408,13 +48426,13 @@
       </c>
       <c r="B2121" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>KPa -&gt; KPA</v>
+        <v>KPa -&gt; kPa</v>
       </c>
       <c r="C2121" t="s">
         <v>570</v>
       </c>
       <c r="D2121" t="s">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="E2121">
         <v>1</v>
@@ -48429,19 +48447,19 @@
       </c>
       <c r="B2122" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>KPa -&gt; Pa</v>
+        <v>KPa -&gt; KPA</v>
       </c>
       <c r="C2122" t="s">
         <v>570</v>
       </c>
       <c r="D2122" t="s">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="E2122">
         <v>1</v>
       </c>
       <c r="F2122">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2123" spans="1:6" x14ac:dyDescent="0.3">
@@ -48450,19 +48468,19 @@
       </c>
       <c r="B2123" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>KPA -&gt; KPa</v>
+        <v>KPa -&gt; Pa</v>
       </c>
       <c r="C2123" t="s">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="D2123" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E2123">
         <v>1</v>
       </c>
       <c r="F2123">
-        <v>1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="2124" spans="1:6" x14ac:dyDescent="0.3">
@@ -48471,13 +48489,13 @@
       </c>
       <c r="B2124" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; J</v>
+        <v>KPA -&gt; KPa</v>
       </c>
       <c r="C2124" t="s">
-        <v>1038</v>
+        <v>599</v>
       </c>
       <c r="D2124" t="s">
-        <v>1039</v>
+        <v>570</v>
       </c>
       <c r="E2124">
         <v>1</v>
@@ -48492,13 +48510,13 @@
       </c>
       <c r="B2125" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; Watt second</v>
+        <v>Joule -&gt; J</v>
       </c>
       <c r="C2125" t="s">
         <v>1038</v>
       </c>
       <c r="D2125" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E2125">
         <v>1</v>
@@ -48513,13 +48531,13 @@
       </c>
       <c r="B2126" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; N*m</v>
+        <v>Joule -&gt; Watt second</v>
       </c>
       <c r="C2126" t="s">
         <v>1038</v>
       </c>
       <c r="D2126" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E2126">
         <v>1</v>
@@ -48534,13 +48552,13 @@
       </c>
       <c r="B2127" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; kg*m2/s2</v>
+        <v>Joule -&gt; N*m</v>
       </c>
       <c r="C2127" t="s">
         <v>1038</v>
       </c>
       <c r="D2127" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E2127">
         <v>1</v>
@@ -48555,13 +48573,13 @@
       </c>
       <c r="B2128" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; Joules</v>
+        <v>Joule -&gt; kg*m2/s2</v>
       </c>
       <c r="C2128" t="s">
         <v>1038</v>
       </c>
       <c r="D2128" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E2128">
         <v>1</v>
@@ -48576,13 +48594,13 @@
       </c>
       <c r="B2129" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; JOULE</v>
+        <v>Joule -&gt; Joules</v>
       </c>
       <c r="C2129" t="s">
         <v>1038</v>
       </c>
       <c r="D2129" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E2129">
         <v>1</v>
@@ -48597,19 +48615,19 @@
       </c>
       <c r="B2130" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; gram calorie</v>
+        <v>Joule -&gt; JOULE</v>
       </c>
       <c r="C2130" t="s">
         <v>1038</v>
       </c>
       <c r="D2130" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E2130">
         <v>1</v>
       </c>
       <c r="F2130">
-        <v>0.23900573613766729</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2131" spans="1:6" x14ac:dyDescent="0.3">
@@ -48618,19 +48636,19 @@
       </c>
       <c r="B2131" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Joule -&gt; Kilojoule</v>
+        <v>Joule -&gt; gram calorie</v>
       </c>
       <c r="C2131" t="s">
         <v>1038</v>
       </c>
       <c r="D2131" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E2131">
         <v>1</v>
       </c>
       <c r="F2131">
-        <v>1E-3</v>
+        <v>0.23900573613766729</v>
       </c>
     </row>
     <row r="2132" spans="1:6" x14ac:dyDescent="0.3">
@@ -48639,19 +48657,19 @@
       </c>
       <c r="B2132" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>J -&gt; Joule</v>
+        <v>Joule -&gt; Kilojoule</v>
       </c>
       <c r="C2132" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D2132" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="E2132">
         <v>1</v>
       </c>
       <c r="F2132">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="2133" spans="1:6" x14ac:dyDescent="0.3">
@@ -48660,13 +48678,13 @@
       </c>
       <c r="B2133" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>J -&gt; J</v>
+        <v>J -&gt; Joule</v>
       </c>
       <c r="C2133" t="s">
         <v>1039</v>
       </c>
       <c r="D2133" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E2133">
         <v>1</v>
@@ -48681,13 +48699,13 @@
       </c>
       <c r="B2134" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Watt second -&gt; Joule</v>
+        <v>J -&gt; J</v>
       </c>
       <c r="C2134" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D2134" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E2134">
         <v>1</v>
@@ -48702,13 +48720,13 @@
       </c>
       <c r="B2135" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Watt second -&gt; Watt*second</v>
+        <v>Watt second -&gt; Joule</v>
       </c>
       <c r="C2135" t="s">
         <v>1040</v>
       </c>
       <c r="D2135" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="E2135">
         <v>1</v>
@@ -48723,13 +48741,13 @@
       </c>
       <c r="B2136" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Watt second -&gt; W*s</v>
+        <v>Watt second -&gt; Watt*second</v>
       </c>
       <c r="C2136" t="s">
         <v>1040</v>
       </c>
       <c r="D2136" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E2136">
         <v>1</v>
@@ -48744,13 +48762,13 @@
       </c>
       <c r="B2137" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Watt second -&gt; Ws</v>
+        <v>Watt second -&gt; W*s</v>
       </c>
       <c r="C2137" t="s">
         <v>1040</v>
       </c>
       <c r="D2137" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E2137">
         <v>1</v>
@@ -48765,13 +48783,13 @@
       </c>
       <c r="B2138" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>Watt second -&gt; WATT SECOND</v>
+        <v>Watt second -&gt; Ws</v>
       </c>
       <c r="C2138" t="s">
         <v>1040</v>
       </c>
       <c r="D2138" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E2138">
         <v>1</v>
@@ -48786,13 +48804,13 @@
       </c>
       <c r="B2139" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>N*m -&gt; Joule</v>
+        <v>Watt second -&gt; WATT SECOND</v>
       </c>
       <c r="C2139" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D2139" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="E2139">
         <v>1</v>
@@ -48807,13 +48825,13 @@
       </c>
       <c r="B2140" s="2" t="str">
         <f t="shared" si="33"/>
-        <v>N*m -&gt; N*M</v>
+        <v>N*m -&gt; Joule</v>
       </c>
       <c r="C2140" t="s">
         <v>1041</v>
       </c>
       <c r="D2140" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="E2140">
         <v>1</v>
@@ -48827,14 +48845,14 @@
         <v>2139</v>
       </c>
       <c r="B2141" s="2" t="str">
-        <f t="shared" ref="B2141:B2204" si="34">C2141&amp;" -&gt; " &amp;D2141</f>
-        <v>kg*m2/s2 -&gt; Joule</v>
+        <f t="shared" si="33"/>
+        <v>N*m -&gt; N*M</v>
       </c>
       <c r="C2141" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D2141" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="E2141">
         <v>1</v>
@@ -48848,14 +48866,14 @@
         <v>2140</v>
       </c>
       <c r="B2142" s="2" t="str">
-        <f t="shared" si="34"/>
-        <v>kg*m2/s2 -&gt; KG*M2/S2</v>
+        <f t="shared" ref="B2142:B2205" si="34">C2142&amp;" -&gt; " &amp;D2142</f>
+        <v>kg*m2/s2 -&gt; Joule</v>
       </c>
       <c r="C2142" t="s">
         <v>1042</v>
       </c>
       <c r="D2142" t="s">
-        <v>1052</v>
+        <v>1038</v>
       </c>
       <c r="E2142">
         <v>1</v>
@@ -48870,13 +48888,13 @@
       </c>
       <c r="B2143" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Joules -&gt; Joule</v>
+        <v>kg*m2/s2 -&gt; KG*M2/S2</v>
       </c>
       <c r="C2143" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D2143" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
       <c r="E2143">
         <v>1</v>
@@ -48891,13 +48909,13 @@
       </c>
       <c r="B2144" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Joules -&gt; JOULES</v>
+        <v>Joules -&gt; Joule</v>
       </c>
       <c r="C2144" t="s">
         <v>1043</v>
       </c>
       <c r="D2144" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="E2144">
         <v>1</v>
@@ -48912,13 +48930,13 @@
       </c>
       <c r="B2145" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Kilojoule -&gt; kJ</v>
+        <v>Joules -&gt; JOULES</v>
       </c>
       <c r="C2145" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D2145" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E2145">
         <v>1</v>
@@ -48933,13 +48951,13 @@
       </c>
       <c r="B2146" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Kilojoule -&gt; KILOJOULE</v>
+        <v>Kilojoule -&gt; kJ</v>
       </c>
       <c r="C2146" t="s">
         <v>1046</v>
       </c>
       <c r="D2146" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E2146">
         <v>1</v>
@@ -48954,19 +48972,19 @@
       </c>
       <c r="B2147" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Kilojoule -&gt; Joule</v>
+        <v>Kilojoule -&gt; KILOJOULE</v>
       </c>
       <c r="C2147" t="s">
         <v>1046</v>
       </c>
       <c r="D2147" t="s">
-        <v>1038</v>
+        <v>1055</v>
       </c>
       <c r="E2147">
         <v>1</v>
       </c>
       <c r="F2147">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2148" spans="1:6" x14ac:dyDescent="0.3">
@@ -48975,19 +48993,19 @@
       </c>
       <c r="B2148" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Kilojoule -&gt; kilowatt hour</v>
+        <v>Kilojoule -&gt; Joule</v>
       </c>
       <c r="C2148" t="s">
         <v>1046</v>
       </c>
       <c r="D2148" t="s">
-        <v>1056</v>
+        <v>1038</v>
       </c>
       <c r="E2148">
         <v>1</v>
       </c>
       <c r="F2148">
-        <v>2.7777777777777778E-4</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="2149" spans="1:6" x14ac:dyDescent="0.3">
@@ -48996,19 +49014,19 @@
       </c>
       <c r="B2149" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Kilojoule -&gt; British thermal unit</v>
+        <v>Kilojoule -&gt; kilowatt hour</v>
       </c>
       <c r="C2149" t="s">
         <v>1046</v>
       </c>
       <c r="D2149" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E2149">
         <v>1</v>
       </c>
       <c r="F2149">
-        <v>0.94786729857819907</v>
+        <v>2.7777777777777778E-4</v>
       </c>
     </row>
     <row r="2150" spans="1:6" x14ac:dyDescent="0.3">
@@ -49017,19 +49035,19 @@
       </c>
       <c r="B2150" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kJ -&gt; Kilojoule</v>
+        <v>Kilojoule -&gt; British thermal unit</v>
       </c>
       <c r="C2150" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="D2150" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="E2150">
         <v>1</v>
       </c>
       <c r="F2150">
-        <v>1</v>
+        <v>0.94786729857819907</v>
       </c>
     </row>
     <row r="2151" spans="1:6" x14ac:dyDescent="0.3">
@@ -49038,13 +49056,13 @@
       </c>
       <c r="B2151" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kJ -&gt; KJ</v>
+        <v>kJ -&gt; Kilojoule</v>
       </c>
       <c r="C2151" t="s">
         <v>1054</v>
       </c>
       <c r="D2151" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
       <c r="E2151">
         <v>1</v>
@@ -49059,13 +49077,13 @@
       </c>
       <c r="B2152" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilowatt hour -&gt; kWh</v>
+        <v>kJ -&gt; KJ</v>
       </c>
       <c r="C2152" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D2152" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E2152">
         <v>1</v>
@@ -49080,13 +49098,13 @@
       </c>
       <c r="B2153" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilowatt hour -&gt; kW*h</v>
+        <v>kilowatt hour -&gt; kWh</v>
       </c>
       <c r="C2153" t="s">
         <v>1056</v>
       </c>
       <c r="D2153" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E2153">
         <v>1</v>
@@ -49101,13 +49119,13 @@
       </c>
       <c r="B2154" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilowatt hour -&gt; kilovatio hora</v>
+        <v>kilowatt hour -&gt; kW*h</v>
       </c>
       <c r="C2154" t="s">
         <v>1056</v>
       </c>
       <c r="D2154" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E2154">
         <v>1</v>
@@ -49122,13 +49140,13 @@
       </c>
       <c r="B2155" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilowatt hour -&gt; KILOWATT HOUR</v>
+        <v>kilowatt hour -&gt; kilovatio hora</v>
       </c>
       <c r="C2155" t="s">
         <v>1056</v>
       </c>
       <c r="D2155" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E2155">
         <v>1</v>
@@ -49143,19 +49161,19 @@
       </c>
       <c r="B2156" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilowatt hour -&gt; Kilojoule</v>
+        <v>kilowatt hour -&gt; KILOWATT HOUR</v>
       </c>
       <c r="C2156" t="s">
         <v>1056</v>
       </c>
       <c r="D2156" t="s">
-        <v>1046</v>
+        <v>1062</v>
       </c>
       <c r="E2156">
         <v>1</v>
       </c>
       <c r="F2156">
-        <v>3600</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2157" spans="1:6" x14ac:dyDescent="0.3">
@@ -49164,19 +49182,19 @@
       </c>
       <c r="B2157" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kWh -&gt; kilowatt hour</v>
+        <v>kilowatt hour -&gt; Kilojoule</v>
       </c>
       <c r="C2157" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D2157" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
       <c r="E2157">
         <v>1</v>
       </c>
       <c r="F2157">
-        <v>1</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="2158" spans="1:6" x14ac:dyDescent="0.3">
@@ -49185,13 +49203,13 @@
       </c>
       <c r="B2158" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kWh -&gt; KWH</v>
+        <v>kWh -&gt; kilowatt hour</v>
       </c>
       <c r="C2158" t="s">
         <v>1059</v>
       </c>
       <c r="D2158" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="E2158">
         <v>1</v>
@@ -49206,13 +49224,13 @@
       </c>
       <c r="B2159" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kW*h -&gt; kilowatt hour</v>
+        <v>kWh -&gt; KWH</v>
       </c>
       <c r="C2159" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D2159" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="E2159">
         <v>1</v>
@@ -49227,13 +49245,13 @@
       </c>
       <c r="B2160" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kW*h -&gt; KW*H</v>
+        <v>kW*h -&gt; kilowatt hour</v>
       </c>
       <c r="C2160" t="s">
         <v>1060</v>
       </c>
       <c r="D2160" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="E2160">
         <v>1</v>
@@ -49248,13 +49266,13 @@
       </c>
       <c r="B2161" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilovatio hora -&gt; kilowatt hour</v>
+        <v>kW*h -&gt; KW*H</v>
       </c>
       <c r="C2161" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D2161" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="E2161">
         <v>1</v>
@@ -49269,13 +49287,13 @@
       </c>
       <c r="B2162" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>kilovatio hora -&gt; KILOVATIO HORA</v>
+        <v>kilovatio hora -&gt; kilowatt hour</v>
       </c>
       <c r="C2162" t="s">
         <v>1061</v>
       </c>
       <c r="D2162" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="E2162">
         <v>1</v>
@@ -49290,13 +49308,13 @@
       </c>
       <c r="B2163" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>British thermal unit -&gt; BTU</v>
+        <v>kilovatio hora -&gt; KILOVATIO HORA</v>
       </c>
       <c r="C2163" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D2163" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E2163">
         <v>1</v>
@@ -49311,13 +49329,13 @@
       </c>
       <c r="B2164" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>British thermal unit -&gt; BRITISH THERMAL UNIT</v>
+        <v>British thermal unit -&gt; BTU</v>
       </c>
       <c r="C2164" t="s">
         <v>1057</v>
       </c>
       <c r="D2164" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E2164">
         <v>1</v>
@@ -49332,19 +49350,19 @@
       </c>
       <c r="B2165" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>British thermal unit -&gt; Kilojoule</v>
+        <v>British thermal unit -&gt; BRITISH THERMAL UNIT</v>
       </c>
       <c r="C2165" t="s">
         <v>1057</v>
       </c>
       <c r="D2165" t="s">
-        <v>1046</v>
+        <v>1067</v>
       </c>
       <c r="E2165">
         <v>1</v>
       </c>
       <c r="F2165">
-        <v>1.0549999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2166" spans="1:6" x14ac:dyDescent="0.3">
@@ -49353,19 +49371,19 @@
       </c>
       <c r="B2166" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>BTU -&gt; British thermal unit</v>
+        <v>British thermal unit -&gt; Kilojoule</v>
       </c>
       <c r="C2166" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="D2166" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
       <c r="E2166">
         <v>1</v>
       </c>
       <c r="F2166">
-        <v>1</v>
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="2167" spans="1:6" x14ac:dyDescent="0.3">
@@ -49374,13 +49392,13 @@
       </c>
       <c r="B2167" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>BTU -&gt; BTU</v>
+        <v>BTU -&gt; British thermal unit</v>
       </c>
       <c r="C2167" t="s">
         <v>1066</v>
       </c>
       <c r="D2167" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="E2167">
         <v>1</v>
@@ -49395,13 +49413,13 @@
       </c>
       <c r="B2168" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Watt*second -&gt; Watt second</v>
+        <v>BTU -&gt; BTU</v>
       </c>
       <c r="C2168" t="s">
-        <v>1047</v>
+        <v>1066</v>
       </c>
       <c r="D2168" t="s">
-        <v>1040</v>
+        <v>1066</v>
       </c>
       <c r="E2168">
         <v>1</v>
@@ -49416,13 +49434,13 @@
       </c>
       <c r="B2169" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Watt*second -&gt; WATT*SECOND</v>
+        <v>Watt*second -&gt; Watt second</v>
       </c>
       <c r="C2169" t="s">
         <v>1047</v>
       </c>
       <c r="D2169" t="s">
-        <v>1068</v>
+        <v>1040</v>
       </c>
       <c r="E2169">
         <v>1</v>
@@ -49437,13 +49455,13 @@
       </c>
       <c r="B2170" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>W*s -&gt; Watt second</v>
+        <v>Watt*second -&gt; WATT*SECOND</v>
       </c>
       <c r="C2170" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D2170" t="s">
-        <v>1040</v>
+        <v>1068</v>
       </c>
       <c r="E2170">
         <v>1</v>
@@ -49458,13 +49476,13 @@
       </c>
       <c r="B2171" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>W*s -&gt; W*S</v>
+        <v>W*s -&gt; Watt second</v>
       </c>
       <c r="C2171" t="s">
         <v>1048</v>
       </c>
       <c r="D2171" t="s">
-        <v>1069</v>
+        <v>1040</v>
       </c>
       <c r="E2171">
         <v>1</v>
@@ -49479,13 +49497,13 @@
       </c>
       <c r="B2172" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Ws -&gt; Watt second</v>
+        <v>W*s -&gt; W*S</v>
       </c>
       <c r="C2172" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D2172" t="s">
-        <v>1040</v>
+        <v>1069</v>
       </c>
       <c r="E2172">
         <v>1</v>
@@ -49500,13 +49518,13 @@
       </c>
       <c r="B2173" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Ws -&gt; WS</v>
+        <v>Ws -&gt; Watt second</v>
       </c>
       <c r="C2173" t="s">
         <v>1049</v>
       </c>
       <c r="D2173" t="s">
-        <v>1070</v>
+        <v>1040</v>
       </c>
       <c r="E2173">
         <v>1</v>
@@ -49521,13 +49539,13 @@
       </c>
       <c r="B2174" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Watt hour -&gt; Wh</v>
+        <v>Ws -&gt; WS</v>
       </c>
       <c r="C2174" t="s">
-        <v>1071</v>
+        <v>1049</v>
       </c>
       <c r="D2174" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E2174">
         <v>1</v>
@@ -49542,13 +49560,13 @@
       </c>
       <c r="B2175" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Watt hour -&gt; W*h</v>
+        <v>Watt hour -&gt; Wh</v>
       </c>
       <c r="C2175" t="s">
         <v>1071</v>
       </c>
       <c r="D2175" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E2175">
         <v>1</v>
@@ -49563,13 +49581,13 @@
       </c>
       <c r="B2176" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Watt hour -&gt; WATT HOUR</v>
+        <v>Watt hour -&gt; W*h</v>
       </c>
       <c r="C2176" t="s">
         <v>1071</v>
       </c>
       <c r="D2176" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E2176">
         <v>1</v>
@@ -49584,13 +49602,13 @@
       </c>
       <c r="B2177" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Wh -&gt; Watt hour</v>
+        <v>Watt hour -&gt; WATT HOUR</v>
       </c>
       <c r="C2177" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D2177" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="E2177">
         <v>1</v>
@@ -49605,13 +49623,13 @@
       </c>
       <c r="B2178" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Wh -&gt; WH</v>
+        <v>Wh -&gt; Watt hour</v>
       </c>
       <c r="C2178" t="s">
         <v>1072</v>
       </c>
       <c r="D2178" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="E2178">
         <v>1</v>
@@ -49626,13 +49644,13 @@
       </c>
       <c r="B2179" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>W*h -&gt; Watt hour</v>
+        <v>Wh -&gt; WH</v>
       </c>
       <c r="C2179" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D2179" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="E2179">
         <v>1</v>
@@ -49647,13 +49665,13 @@
       </c>
       <c r="B2180" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>W*h -&gt; W*H</v>
+        <v>W*h -&gt; Watt hour</v>
       </c>
       <c r="C2180" t="s">
         <v>1073</v>
       </c>
       <c r="D2180" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="E2180">
         <v>1</v>
@@ -49668,13 +49686,13 @@
       </c>
       <c r="B2181" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>gram calorie -&gt; cal</v>
+        <v>W*h -&gt; W*H</v>
       </c>
       <c r="C2181" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="D2181" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E2181">
         <v>1</v>
@@ -49689,13 +49707,13 @@
       </c>
       <c r="B2182" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>gram calorie -&gt; calorie</v>
+        <v>gram calorie -&gt; cal</v>
       </c>
       <c r="C2182" t="s">
         <v>1045</v>
       </c>
       <c r="D2182" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E2182">
         <v>1</v>
@@ -49710,13 +49728,13 @@
       </c>
       <c r="B2183" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>gram calorie -&gt; Calorie</v>
+        <v>gram calorie -&gt; calorie</v>
       </c>
       <c r="C2183" t="s">
         <v>1045</v>
       </c>
       <c r="D2183" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E2183">
         <v>1</v>
@@ -49731,13 +49749,13 @@
       </c>
       <c r="B2184" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>gram calorie -&gt; GRAM CALORIE</v>
+        <v>gram calorie -&gt; Calorie</v>
       </c>
       <c r="C2184" t="s">
         <v>1045</v>
       </c>
       <c r="D2184" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E2184">
         <v>1</v>
@@ -49752,19 +49770,19 @@
       </c>
       <c r="B2185" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>gram calorie -&gt; Joule</v>
+        <v>gram calorie -&gt; GRAM CALORIE</v>
       </c>
       <c r="C2185" t="s">
         <v>1045</v>
       </c>
       <c r="D2185" t="s">
-        <v>1038</v>
+        <v>1080</v>
       </c>
       <c r="E2185">
         <v>1</v>
       </c>
       <c r="F2185">
-        <v>4.1840000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2186" spans="1:6" x14ac:dyDescent="0.3">
@@ -49773,19 +49791,19 @@
       </c>
       <c r="B2186" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>cal -&gt; gram calorie</v>
+        <v>gram calorie -&gt; Joule</v>
       </c>
       <c r="C2186" t="s">
-        <v>1077</v>
+        <v>1045</v>
       </c>
       <c r="D2186" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="E2186">
         <v>1</v>
       </c>
       <c r="F2186">
-        <v>1</v>
+        <v>4.1840000000000002</v>
       </c>
     </row>
     <row r="2187" spans="1:6" x14ac:dyDescent="0.3">
@@ -49794,13 +49812,13 @@
       </c>
       <c r="B2187" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>cal -&gt; CAL</v>
+        <v>cal -&gt; gram calorie</v>
       </c>
       <c r="C2187" t="s">
         <v>1077</v>
       </c>
       <c r="D2187" t="s">
-        <v>1081</v>
+        <v>1045</v>
       </c>
       <c r="E2187">
         <v>1</v>
@@ -49815,13 +49833,13 @@
       </c>
       <c r="B2188" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>calorie -&gt; gram calorie</v>
+        <v>cal -&gt; CAL</v>
       </c>
       <c r="C2188" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D2188" t="s">
-        <v>1045</v>
+        <v>1081</v>
       </c>
       <c r="E2188">
         <v>1</v>
@@ -49836,13 +49854,13 @@
       </c>
       <c r="B2189" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>calorie -&gt; CALORIE</v>
+        <v>calorie -&gt; gram calorie</v>
       </c>
       <c r="C2189" t="s">
         <v>1078</v>
       </c>
       <c r="D2189" t="s">
-        <v>1082</v>
+        <v>1045</v>
       </c>
       <c r="E2189">
         <v>1</v>
@@ -49857,13 +49875,13 @@
       </c>
       <c r="B2190" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Calorie -&gt; gram calorie</v>
+        <v>calorie -&gt; CALORIE</v>
       </c>
       <c r="C2190" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D2190" t="s">
-        <v>1045</v>
+        <v>1082</v>
       </c>
       <c r="E2190">
         <v>1</v>
@@ -49878,13 +49896,13 @@
       </c>
       <c r="B2191" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>Calorie -&gt; CALORIE</v>
+        <v>Calorie -&gt; gram calorie</v>
       </c>
       <c r="C2191" t="s">
         <v>1079</v>
       </c>
       <c r="D2191" t="s">
-        <v>1082</v>
+        <v>1045</v>
       </c>
       <c r="E2191">
         <v>1</v>
@@ -49899,13 +49917,13 @@
       </c>
       <c r="B2192" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>JOULE -&gt; Joule</v>
+        <v>Calorie -&gt; CALORIE</v>
       </c>
       <c r="C2192" t="s">
-        <v>1044</v>
+        <v>1079</v>
       </c>
       <c r="D2192" t="s">
-        <v>1038</v>
+        <v>1082</v>
       </c>
       <c r="E2192">
         <v>1</v>
@@ -49920,13 +49938,13 @@
       </c>
       <c r="B2193" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>WATT SECOND -&gt; Watt second</v>
+        <v>JOULE -&gt; Joule</v>
       </c>
       <c r="C2193" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="D2193" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E2193">
         <v>1</v>
@@ -49941,13 +49959,13 @@
       </c>
       <c r="B2194" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>N*M -&gt; N*m</v>
+        <v>WATT SECOND -&gt; Watt second</v>
       </c>
       <c r="C2194" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D2194" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E2194">
         <v>1</v>
@@ -49962,13 +49980,13 @@
       </c>
       <c r="B2195" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KG*M2/S2 -&gt; kg*m2/s2</v>
+        <v>N*M -&gt; N*m</v>
       </c>
       <c r="C2195" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D2195" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E2195">
         <v>1</v>
@@ -49983,13 +50001,13 @@
       </c>
       <c r="B2196" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>JOULES -&gt; Joules</v>
+        <v>KG*M2/S2 -&gt; kg*m2/s2</v>
       </c>
       <c r="C2196" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D2196" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E2196">
         <v>1</v>
@@ -50004,13 +50022,13 @@
       </c>
       <c r="B2197" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KILOJOULE -&gt; Kilojoule</v>
+        <v>JOULES -&gt; Joules</v>
       </c>
       <c r="C2197" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D2197" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="E2197">
         <v>1</v>
@@ -50025,13 +50043,13 @@
       </c>
       <c r="B2198" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KJ -&gt; kJ</v>
+        <v>KILOJOULE -&gt; Kilojoule</v>
       </c>
       <c r="C2198" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="D2198" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="E2198">
         <v>1</v>
@@ -50046,13 +50064,13 @@
       </c>
       <c r="B2199" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KILOWATT HOUR -&gt; kilowatt hour</v>
+        <v>KJ -&gt; kJ</v>
       </c>
       <c r="C2199" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="D2199" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E2199">
         <v>1</v>
@@ -50067,13 +50085,13 @@
       </c>
       <c r="B2200" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KWH -&gt; kWh</v>
+        <v>KILOWATT HOUR -&gt; kilowatt hour</v>
       </c>
       <c r="C2200" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D2200" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E2200">
         <v>1</v>
@@ -50088,13 +50106,13 @@
       </c>
       <c r="B2201" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KW*H -&gt; kW*h</v>
+        <v>KWH -&gt; kWh</v>
       </c>
       <c r="C2201" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D2201" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E2201">
         <v>1</v>
@@ -50109,13 +50127,13 @@
       </c>
       <c r="B2202" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>KILOVATIO HORA -&gt; kilovatio hora</v>
+        <v>KW*H -&gt; kW*h</v>
       </c>
       <c r="C2202" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D2202" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E2202">
         <v>1</v>
@@ -50130,13 +50148,13 @@
       </c>
       <c r="B2203" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>BRITISH THERMAL UNIT -&gt; British thermal unit</v>
+        <v>KILOVATIO HORA -&gt; kilovatio hora</v>
       </c>
       <c r="C2203" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D2203" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="E2203">
         <v>1</v>
@@ -50151,13 +50169,13 @@
       </c>
       <c r="B2204" s="2" t="str">
         <f t="shared" si="34"/>
-        <v>WATT*SECOND -&gt; Watt*second</v>
+        <v>BRITISH THERMAL UNIT -&gt; British thermal unit</v>
       </c>
       <c r="C2204" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D2204" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="E2204">
         <v>1</v>
@@ -50171,14 +50189,14 @@
         <v>2203</v>
       </c>
       <c r="B2205" s="2" t="str">
-        <f t="shared" ref="B2205:B2261" si="35">C2205&amp;" -&gt; " &amp;D2205</f>
-        <v>W*S -&gt; W*s</v>
+        <f t="shared" si="34"/>
+        <v>WATT*SECOND -&gt; Watt*second</v>
       </c>
       <c r="C2205" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D2205" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E2205">
         <v>1</v>
@@ -50192,14 +50210,14 @@
         <v>2204</v>
       </c>
       <c r="B2206" s="2" t="str">
-        <f t="shared" si="35"/>
-        <v>WS -&gt; Ws</v>
+        <f t="shared" ref="B2206:B2262" si="35">C2206&amp;" -&gt; " &amp;D2206</f>
+        <v>W*S -&gt; W*s</v>
       </c>
       <c r="C2206" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D2206" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E2206">
         <v>1</v>
@@ -50214,13 +50232,13 @@
       </c>
       <c r="B2207" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>WATT HOUR -&gt; Watt hour</v>
+        <v>WS -&gt; Ws</v>
       </c>
       <c r="C2207" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="D2207" t="s">
-        <v>1071</v>
+        <v>1049</v>
       </c>
       <c r="E2207">
         <v>1</v>
@@ -50235,13 +50253,13 @@
       </c>
       <c r="B2208" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>WH -&gt; Wh</v>
+        <v>WATT HOUR -&gt; Watt hour</v>
       </c>
       <c r="C2208" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D2208" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E2208">
         <v>1</v>
@@ -50256,13 +50274,13 @@
       </c>
       <c r="B2209" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>W*H -&gt; W*h</v>
+        <v>WH -&gt; Wh</v>
       </c>
       <c r="C2209" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D2209" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E2209">
         <v>1</v>
@@ -50277,13 +50295,13 @@
       </c>
       <c r="B2210" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>GRAM CALORIE -&gt; gram calorie</v>
+        <v>W*H -&gt; W*h</v>
       </c>
       <c r="C2210" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="D2210" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="E2210">
         <v>1</v>
@@ -50298,13 +50316,13 @@
       </c>
       <c r="B2211" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>CAL -&gt; cal</v>
+        <v>GRAM CALORIE -&gt; gram calorie</v>
       </c>
       <c r="C2211" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D2211" t="s">
-        <v>1077</v>
+        <v>1045</v>
       </c>
       <c r="E2211">
         <v>1</v>
@@ -50319,13 +50337,13 @@
       </c>
       <c r="B2212" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>CALORIE -&gt; calorie</v>
+        <v>CAL -&gt; cal</v>
       </c>
       <c r="C2212" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D2212" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E2212">
         <v>1</v>
@@ -50340,13 +50358,13 @@
       </c>
       <c r="B2213" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>CALORIE -&gt; Calorie</v>
+        <v>CALORIE -&gt; calorie</v>
       </c>
       <c r="C2213" t="s">
         <v>1082</v>
       </c>
       <c r="D2213" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E2213">
         <v>1</v>
@@ -50361,13 +50379,13 @@
       </c>
       <c r="B2214" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Horsepower -&gt; hp</v>
+        <v>CALORIE -&gt; Calorie</v>
       </c>
       <c r="C2214" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D2214" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="E2214">
         <v>1</v>
@@ -50382,13 +50400,13 @@
       </c>
       <c r="B2215" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Horsepower -&gt; HORSEPOWER</v>
+        <v>Horsepower -&gt; hp</v>
       </c>
       <c r="C2215" t="s">
         <v>1083</v>
       </c>
       <c r="D2215" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E2215">
         <v>1</v>
@@ -50403,19 +50421,19 @@
       </c>
       <c r="B2216" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Horsepower -&gt; Watt</v>
+        <v>Horsepower -&gt; HORSEPOWER</v>
       </c>
       <c r="C2216" t="s">
         <v>1083</v>
       </c>
       <c r="D2216" t="s">
-        <v>1010</v>
+        <v>1085</v>
       </c>
       <c r="E2216">
         <v>1</v>
       </c>
       <c r="F2216">
-        <v>745.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2217" spans="1:6" x14ac:dyDescent="0.3">
@@ -50424,19 +50442,19 @@
       </c>
       <c r="B2217" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>hp -&gt; Horsepower</v>
+        <v>Horsepower -&gt; Watt</v>
       </c>
       <c r="C2217" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D2217" t="s">
-        <v>1083</v>
+        <v>1010</v>
       </c>
       <c r="E2217">
         <v>1</v>
       </c>
       <c r="F2217">
-        <v>1</v>
+        <v>745.7</v>
       </c>
     </row>
     <row r="2218" spans="1:6" x14ac:dyDescent="0.3">
@@ -50445,13 +50463,13 @@
       </c>
       <c r="B2218" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>hp -&gt; HP</v>
+        <v>hp -&gt; Horsepower</v>
       </c>
       <c r="C2218" t="s">
         <v>1084</v>
       </c>
       <c r="D2218" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="E2218">
         <v>1</v>
@@ -50466,13 +50484,13 @@
       </c>
       <c r="B2219" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Watt -&gt; W</v>
+        <v>hp -&gt; HP</v>
       </c>
       <c r="C2219" t="s">
-        <v>1010</v>
+        <v>1084</v>
       </c>
       <c r="D2219" t="s">
-        <v>70</v>
+        <v>1086</v>
       </c>
       <c r="E2219">
         <v>1</v>
@@ -50487,13 +50505,13 @@
       </c>
       <c r="B2220" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Watt -&gt; J/s</v>
+        <v>Watt -&gt; W</v>
       </c>
       <c r="C2220" t="s">
         <v>1010</v>
       </c>
       <c r="D2220" t="s">
-        <v>1087</v>
+        <v>70</v>
       </c>
       <c r="E2220">
         <v>1</v>
@@ -50508,13 +50526,13 @@
       </c>
       <c r="B2221" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Watt -&gt; WATT</v>
+        <v>Watt -&gt; J/s</v>
       </c>
       <c r="C2221" t="s">
         <v>1010</v>
       </c>
       <c r="D2221" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E2221">
         <v>1</v>
@@ -50529,19 +50547,19 @@
       </c>
       <c r="B2222" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>Watt -&gt; Horsepower</v>
+        <v>Watt -&gt; WATT</v>
       </c>
       <c r="C2222" t="s">
         <v>1010</v>
       </c>
       <c r="D2222" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="E2222">
         <v>1</v>
       </c>
       <c r="F2222">
-        <v>1.341021858656296E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2223" spans="1:6" x14ac:dyDescent="0.3">
@@ -50550,19 +50568,19 @@
       </c>
       <c r="B2223" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>J/s -&gt; Watt</v>
+        <v>Watt -&gt; Horsepower</v>
       </c>
       <c r="C2223" t="s">
-        <v>1087</v>
+        <v>1010</v>
       </c>
       <c r="D2223" t="s">
-        <v>1010</v>
+        <v>1083</v>
       </c>
       <c r="E2223">
         <v>1</v>
       </c>
       <c r="F2223">
-        <v>1</v>
+        <v>1.341021858656296E-3</v>
       </c>
     </row>
     <row r="2224" spans="1:6" x14ac:dyDescent="0.3">
@@ -50571,13 +50589,13 @@
       </c>
       <c r="B2224" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>J/s -&gt; J/S</v>
+        <v>J/s -&gt; Watt</v>
       </c>
       <c r="C2224" t="s">
         <v>1087</v>
       </c>
       <c r="D2224" t="s">
-        <v>1089</v>
+        <v>1010</v>
       </c>
       <c r="E2224">
         <v>1</v>
@@ -50592,13 +50610,13 @@
       </c>
       <c r="B2225" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>HORSEPOWER -&gt; Horsepower</v>
+        <v>J/s -&gt; J/S</v>
       </c>
       <c r="C2225" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D2225" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="E2225">
         <v>1</v>
@@ -50613,13 +50631,13 @@
       </c>
       <c r="B2226" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>HP -&gt; hp</v>
+        <v>HORSEPOWER -&gt; Horsepower</v>
       </c>
       <c r="C2226" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D2226" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E2226">
         <v>1</v>
@@ -50634,13 +50652,13 @@
       </c>
       <c r="B2227" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>WATT -&gt; Watt</v>
+        <v>HP -&gt; hp</v>
       </c>
       <c r="C2227" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D2227" t="s">
-        <v>1010</v>
+        <v>1084</v>
       </c>
       <c r="E2227">
         <v>1</v>
@@ -50655,13 +50673,13 @@
       </c>
       <c r="B2228" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>J/S -&gt; J/s</v>
+        <v>WATT -&gt; Watt</v>
       </c>
       <c r="C2228" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D2228" t="s">
-        <v>1087</v>
+        <v>1010</v>
       </c>
       <c r="E2228">
         <v>1</v>
@@ -50676,13 +50694,13 @@
       </c>
       <c r="B2229" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>stb/day/psi -&gt; STB/DAY-PSI</v>
+        <v>J/S -&gt; J/s</v>
       </c>
       <c r="C2229" t="s">
-        <v>946</v>
+        <v>1089</v>
       </c>
       <c r="D2229" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="E2229">
         <v>1</v>
@@ -50697,13 +50715,13 @@
       </c>
       <c r="B2230" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>stb/day/psi -&gt; STB/DAY-PSIA</v>
+        <v>stb/day/psi -&gt; STB/DAY-PSI</v>
       </c>
       <c r="C2230" t="s">
         <v>946</v>
       </c>
       <c r="D2230" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E2230">
         <v>1</v>
@@ -50718,13 +50736,13 @@
       </c>
       <c r="B2231" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>STB/DAY-PSI -&gt; stb/day/psi</v>
+        <v>stb/day/psi -&gt; STB/DAY-PSIA</v>
       </c>
       <c r="C2231" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="D2231" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="E2231">
         <v>1</v>
@@ -50739,13 +50757,13 @@
       </c>
       <c r="B2232" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>STB/DAY-PSI -&gt; STB/DAY-PSI</v>
+        <v>STB/DAY-PSI -&gt; stb/day/psi</v>
       </c>
       <c r="C2232" t="s">
         <v>966</v>
       </c>
       <c r="D2232" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
       <c r="E2232">
         <v>1</v>
@@ -50760,13 +50778,13 @@
       </c>
       <c r="B2233" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>STB/DAY-PSIA -&gt; stb/day/psi</v>
+        <v>STB/DAY-PSI -&gt; STB/DAY-PSI</v>
       </c>
       <c r="C2233" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D2233" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="E2233">
         <v>1</v>
@@ -50781,13 +50799,13 @@
       </c>
       <c r="B2234" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>STB/DAY-PSIA -&gt; STB/DAY-PSIA</v>
+        <v>STB/DAY-PSIA -&gt; stb/day/psi</v>
       </c>
       <c r="C2234" t="s">
         <v>967</v>
       </c>
       <c r="D2234" t="s">
-        <v>967</v>
+        <v>946</v>
       </c>
       <c r="E2234">
         <v>1</v>
@@ -50802,13 +50820,13 @@
       </c>
       <c r="B2235" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>sm3/day/bar -&gt; SM3/DAY-BAR</v>
+        <v>STB/DAY-PSIA -&gt; STB/DAY-PSIA</v>
       </c>
       <c r="C2235" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="D2235" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="E2235">
         <v>1</v>
@@ -50823,13 +50841,13 @@
       </c>
       <c r="B2236" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>sm3/day/bar -&gt; SM3/DAY-BARA</v>
+        <v>sm3/day/bar -&gt; SM3/DAY-BAR</v>
       </c>
       <c r="C2236" t="s">
         <v>954</v>
       </c>
       <c r="D2236" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E2236">
         <v>1</v>
@@ -50844,13 +50862,13 @@
       </c>
       <c r="B2237" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>sm3/day/bar -&gt; sm3/day/barsa</v>
+        <v>sm3/day/bar -&gt; SM3/DAY-BARA</v>
       </c>
       <c r="C2237" t="s">
         <v>954</v>
       </c>
       <c r="D2237" t="s">
-        <v>1090</v>
+        <v>975</v>
       </c>
       <c r="E2237">
         <v>1</v>
@@ -50865,13 +50883,13 @@
       </c>
       <c r="B2238" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY-BAR -&gt; sm3/day/bar</v>
+        <v>sm3/day/bar -&gt; sm3/day/barsa</v>
       </c>
       <c r="C2238" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="D2238" t="s">
-        <v>954</v>
+        <v>1090</v>
       </c>
       <c r="E2238">
         <v>1</v>
@@ -50886,13 +50904,13 @@
       </c>
       <c r="B2239" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY-BAR -&gt; SM3/DAY-BAR</v>
+        <v>SM3/DAY-BAR -&gt; sm3/day/bar</v>
       </c>
       <c r="C2239" t="s">
         <v>974</v>
       </c>
       <c r="D2239" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="E2239">
         <v>1</v>
@@ -50907,13 +50925,13 @@
       </c>
       <c r="B2240" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY-BARA -&gt; sm3/day/bar</v>
+        <v>SM3/DAY-BAR -&gt; SM3/DAY-BAR</v>
       </c>
       <c r="C2240" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D2240" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
       <c r="E2240">
         <v>1</v>
@@ -50928,13 +50946,13 @@
       </c>
       <c r="B2241" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY-BARA -&gt; SM3/DAY-BARA</v>
+        <v>SM3/DAY-BARA -&gt; sm3/day/bar</v>
       </c>
       <c r="C2241" t="s">
         <v>975</v>
       </c>
       <c r="D2241" t="s">
-        <v>975</v>
+        <v>954</v>
       </c>
       <c r="E2241">
         <v>1</v>
@@ -50949,13 +50967,13 @@
       </c>
       <c r="B2242" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>sm3/day/barsa -&gt; sm3/day/bar</v>
+        <v>SM3/DAY-BARA -&gt; SM3/DAY-BARA</v>
       </c>
       <c r="C2242" t="s">
-        <v>1090</v>
+        <v>975</v>
       </c>
       <c r="D2242" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="E2242">
         <v>1</v>
@@ -50970,13 +50988,13 @@
       </c>
       <c r="B2243" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>sm3/day/barsa -&gt; SM3/DAY/BARSA</v>
+        <v>sm3/day/barsa -&gt; sm3/day/bar</v>
       </c>
       <c r="C2243" t="s">
         <v>1090</v>
       </c>
       <c r="D2243" t="s">
-        <v>1091</v>
+        <v>954</v>
       </c>
       <c r="E2243">
         <v>1</v>
@@ -50991,13 +51009,13 @@
       </c>
       <c r="B2244" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>sm3/day/kPa -&gt; SM3/DAY-KPA</v>
+        <v>sm3/day/barsa -&gt; SM3/DAY/BARSA</v>
       </c>
       <c r="C2244" t="s">
-        <v>1007</v>
+        <v>1090</v>
       </c>
       <c r="D2244" t="s">
-        <v>978</v>
+        <v>1091</v>
       </c>
       <c r="E2244">
         <v>1</v>
@@ -51012,13 +51030,13 @@
       </c>
       <c r="B2245" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY-KPA -&gt; sm3/day/kPa</v>
+        <v>sm3/day/kPa -&gt; SM3/DAY-KPA</v>
       </c>
       <c r="C2245" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D2245" t="s">
         <v>978</v>
-      </c>
-      <c r="D2245" t="s">
-        <v>1007</v>
       </c>
       <c r="E2245">
         <v>1</v>
@@ -51033,13 +51051,13 @@
       </c>
       <c r="B2246" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY-KPA -&gt; SM3/DAY-KPA</v>
+        <v>SM3/DAY-KPA -&gt; sm3/day/kPa</v>
       </c>
       <c r="C2246" t="s">
         <v>978</v>
       </c>
       <c r="D2246" t="s">
-        <v>978</v>
+        <v>1007</v>
       </c>
       <c r="E2246">
         <v>1</v>
@@ -51054,13 +51072,13 @@
       </c>
       <c r="B2247" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>SM3/DAY/BARSA -&gt; sm3/day/barsa</v>
+        <v>SM3/DAY-KPA -&gt; SM3/DAY-KPA</v>
       </c>
       <c r="C2247" t="s">
-        <v>1091</v>
+        <v>978</v>
       </c>
       <c r="D2247" t="s">
-        <v>1090</v>
+        <v>978</v>
       </c>
       <c r="E2247">
         <v>1</v>
@@ -51075,19 +51093,19 @@
       </c>
       <c r="B2248" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>F/ft -&gt; C/m</v>
+        <v>SM3/DAY/BARSA -&gt; sm3/day/barsa</v>
       </c>
       <c r="C2248" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D2248" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E2248">
         <v>1</v>
       </c>
       <c r="F2248">
-        <v>1.8226888305628459</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2249" spans="1:6" x14ac:dyDescent="0.3">
@@ -51096,19 +51114,19 @@
       </c>
       <c r="B2249" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>C/m -&gt; F/ft</v>
+        <v>F/ft -&gt; C/m</v>
       </c>
       <c r="C2249" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D2249" t="s">
         <v>1093</v>
       </c>
-      <c r="D2249" t="s">
-        <v>1092</v>
-      </c>
       <c r="E2249">
         <v>1</v>
       </c>
       <c r="F2249">
-        <v>0.54864000000000013</v>
+        <v>1.8226888305628459</v>
       </c>
     </row>
     <row r="2250" spans="1:6" x14ac:dyDescent="0.3">
@@ -51117,19 +51135,19 @@
       </c>
       <c r="B2250" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>F/yd -&gt; F/in</v>
+        <v>C/m -&gt; F/ft</v>
       </c>
       <c r="C2250" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="D2250" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="E2250">
         <v>1</v>
       </c>
       <c r="F2250">
-        <v>2.777777777777778E-2</v>
+        <v>0.54864000000000013</v>
       </c>
     </row>
     <row r="2251" spans="1:6" x14ac:dyDescent="0.3">
@@ -51138,19 +51156,19 @@
       </c>
       <c r="B2251" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>F/ft -&gt; C/km</v>
+        <v>F/yd -&gt; F/in</v>
       </c>
       <c r="C2251" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D2251" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E2251">
         <v>1</v>
       </c>
       <c r="F2251">
-        <v>1822.6888305628461</v>
+        <v>2.777777777777778E-2</v>
       </c>
     </row>
     <row r="2252" spans="1:6" x14ac:dyDescent="0.3">
@@ -51159,19 +51177,19 @@
       </c>
       <c r="B2252" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>K/m -&gt; C/m</v>
+        <v>F/ft -&gt; C/km</v>
       </c>
       <c r="C2252" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="D2252" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="E2252">
         <v>1</v>
       </c>
       <c r="F2252">
-        <v>1</v>
+        <v>1822.6888305628461</v>
       </c>
     </row>
     <row r="2253" spans="1:6" x14ac:dyDescent="0.3">
@@ -51180,19 +51198,19 @@
       </c>
       <c r="B2253" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>K/m -&gt; C/cm</v>
+        <v>K/m -&gt; C/m</v>
       </c>
       <c r="C2253" t="s">
         <v>1097</v>
       </c>
       <c r="D2253" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="E2253">
         <v>1</v>
       </c>
       <c r="F2253">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2254" spans="1:6" x14ac:dyDescent="0.3">
@@ -51201,19 +51219,19 @@
       </c>
       <c r="B2254" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>C/min -&gt; C/hour</v>
+        <v>K/m -&gt; C/cm</v>
       </c>
       <c r="C2254" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D2254" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="E2254">
         <v>1</v>
       </c>
       <c r="F2254">
-        <v>60</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="2255" spans="1:6" x14ac:dyDescent="0.3">
@@ -51222,19 +51240,19 @@
       </c>
       <c r="B2255" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>C/day -&gt; F/s</v>
+        <v>C/min -&gt; C/hour</v>
       </c>
       <c r="C2255" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D2255" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E2255">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="F2255">
-        <v>5.208333333333333E-3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2256" spans="1:6" x14ac:dyDescent="0.3">
@@ -51243,19 +51261,19 @@
       </c>
       <c r="B2256" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>MPH -&gt; KPH</v>
+        <v>C/day -&gt; F/s</v>
       </c>
       <c r="C2256" t="s">
-        <v>1122</v>
+        <v>1100</v>
       </c>
       <c r="D2256" t="s">
-        <v>1123</v>
+        <v>1102</v>
       </c>
       <c r="E2256">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F2256">
-        <v>96.560640000000006</v>
+        <v>5.208333333333333E-3</v>
       </c>
     </row>
     <row r="2257" spans="1:6" x14ac:dyDescent="0.3">
@@ -51264,19 +51282,19 @@
       </c>
       <c r="B2257" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>mph -&gt; ft/sec</v>
+        <v>MPH -&gt; KPH</v>
       </c>
       <c r="C2257" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="D2257" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="E2257">
         <v>60</v>
       </c>
       <c r="F2257">
-        <v>88</v>
+        <v>96.560640000000006</v>
       </c>
     </row>
     <row r="2258" spans="1:6" x14ac:dyDescent="0.3">
@@ -51285,19 +51303,19 @@
       </c>
       <c r="B2258" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>kph -&gt; km/day</v>
+        <v>mph -&gt; ft/sec</v>
       </c>
       <c r="C2258" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D2258" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="E2258">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F2258">
-        <v>24</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2259" spans="1:6" x14ac:dyDescent="0.3">
@@ -51306,19 +51324,19 @@
       </c>
       <c r="B2259" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>kg/m3 -&gt; psi/ft</v>
+        <v>kph -&gt; km/day</v>
       </c>
       <c r="C2259" t="s">
-        <v>841</v>
+        <v>1126</v>
       </c>
       <c r="D2259" t="s">
-        <v>844</v>
+        <v>1127</v>
       </c>
       <c r="E2259">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F2259">
-        <v>0.43352750400100398</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2260" spans="1:6" x14ac:dyDescent="0.3">
@@ -51327,20 +51345,19 @@
       </c>
       <c r="B2260" s="2" t="str">
         <f t="shared" si="35"/>
-        <v>kg/m3 -&gt; bar/m</v>
+        <v>kg/m3 -&gt; psi/ft</v>
       </c>
       <c r="C2260" t="s">
         <v>841</v>
       </c>
       <c r="D2260" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E2260">
         <v>1000</v>
       </c>
       <c r="F2260">
-        <f>E2260/100000*9.80665</f>
-        <v>9.8066500000000001E-2</v>
+        <v>0.43352750400100398</v>
       </c>
     </row>
     <row r="2261" spans="1:6" x14ac:dyDescent="0.3">
@@ -51349,23 +51366,45 @@
       </c>
       <c r="B2261" s="2" t="str">
         <f t="shared" si="35"/>
+        <v>kg/m3 -&gt; bar/m</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>841</v>
+      </c>
+      <c r="D2261" t="s">
+        <v>848</v>
+      </c>
+      <c r="E2261">
+        <v>1000</v>
+      </c>
+      <c r="F2261">
+        <f>E2261/100000*9.80665</f>
+        <v>9.8066500000000001E-2</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2262" s="1">
+        <v>2260</v>
+      </c>
+      <c r="B2262" s="2" t="str">
+        <f t="shared" si="35"/>
         <v>lb/ft3 -&gt; psi/ft</v>
       </c>
-      <c r="C2261" t="s">
+      <c r="C2262" t="s">
         <v>843</v>
       </c>
-      <c r="D2261" t="s">
+      <c r="D2262" t="s">
         <v>844</v>
       </c>
-      <c r="E2261">
+      <c r="E2262">
         <v>65</v>
       </c>
-      <c r="F2261">
+      <c r="F2262">
         <v>0.45138888888888801</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2255" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F2256" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/tests/conversions_check.xlsx
+++ b/tests/conversions_check.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\unyts\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E99D13-D002-46AC-BEE2-DEA0C6B4C2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC8A7CC-0F9C-490E-A22C-AEBF66E7F3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49176" yWindow="2160" windowWidth="36156" windowHeight="19512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45972" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2256</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2265</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4532" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4596" uniqueCount="1177">
   <si>
     <t>source</t>
   </si>
@@ -3526,6 +3526,45 @@
   </si>
   <si>
     <t>sip</t>
+  </si>
+  <si>
+    <t>MPa/km</t>
+  </si>
+  <si>
+    <t>cm3/min/Pa</t>
+  </si>
+  <si>
+    <t>sm3/day/psi</t>
+  </si>
+  <si>
+    <t>scf/day/psi</t>
+  </si>
+  <si>
+    <t>cc/min/Torr</t>
+  </si>
+  <si>
+    <t>kPa/m</t>
+  </si>
+  <si>
+    <t>Pa/m</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>km/h</t>
+  </si>
+  <si>
+    <t>mD</t>
+  </si>
+  <si>
+    <t>scf/stb</t>
+  </si>
+  <si>
+    <t>sm3/sm3</t>
+  </si>
+  <si>
+    <t>psig/ft</t>
   </si>
 </sst>
 </file>
@@ -3885,12 +3924,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2262"/>
+  <dimension ref="A1:G2294"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="4" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -45318,10 +45357,10 @@
       </c>
       <c r="B1973" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/ -&gt; sm3/day/bar</v>
+        <v>SM3/DAY/BAR -&gt; sm3/day/bar</v>
       </c>
       <c r="C1973" t="s">
-        <v>955</v>
+        <v>969</v>
       </c>
       <c r="D1973" t="s">
         <v>954</v>
@@ -45339,13 +45378,13 @@
       </c>
       <c r="B1974" s="2" t="str">
         <f t="shared" si="31"/>
-        <v>SM3/DAY/ -&gt; SM3/DAY/</v>
+        <v>SM3/DAY/BARA -&gt; SM3/DAY/BARSA</v>
       </c>
       <c r="C1974" t="s">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="D1974" t="s">
-        <v>955</v>
+        <v>1091</v>
       </c>
       <c r="E1974">
         <v>1</v>
@@ -51378,7 +51417,6 @@
         <v>1000</v>
       </c>
       <c r="F2261">
-        <f>E2261/100000*9.80665</f>
         <v>9.8066500000000001E-2</v>
       </c>
     </row>
@@ -51403,8 +51441,680 @@
         <v>0.45138888888888801</v>
       </c>
     </row>
+    <row r="2263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2263" s="1">
+        <v>2261</v>
+      </c>
+      <c r="B2263" s="2" t="str">
+        <f t="shared" ref="B2263:B2265" si="36">C2263&amp;" -&gt; " &amp;D2263</f>
+        <v>g/cc -&gt; MPa/km</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>840</v>
+      </c>
+      <c r="D2263" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E2263">
+        <v>1</v>
+      </c>
+      <c r="F2263">
+        <v>9.8066499998653907</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2264" s="1">
+        <v>2262</v>
+      </c>
+      <c r="B2264" s="2" t="str">
+        <f t="shared" si="36"/>
+        <v>cm3/min/Pa -&gt; sm3/day/psi</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E2264">
+        <v>1</v>
+      </c>
+      <c r="F2264">
+        <v>9.9284505020261609</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2265" s="1">
+        <v>2263</v>
+      </c>
+      <c r="B2265" s="2" t="str">
+        <f t="shared" si="36"/>
+        <v>cc/min/Torr -&gt; scf/day/psi</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D2265" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E2265">
+        <v>1</v>
+      </c>
+      <c r="F2265">
+        <v>2.6298656758972201</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2266" s="1">
+        <v>2264</v>
+      </c>
+      <c r="B2266" s="2" t="str">
+        <f t="shared" ref="B2266:B2277" si="37">C2266&amp;" -&gt; " &amp;D2266</f>
+        <v>lb/ft3 -&gt; MPa/km</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>843</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E2266">
+        <v>1</v>
+      </c>
+      <c r="F2266">
+        <v>0.15708746384408959</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2267" s="1">
+        <v>2265</v>
+      </c>
+      <c r="B2267" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>bara/m -&gt; MPa/km</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>847</v>
+      </c>
+      <c r="D2267" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E2267">
+        <v>1</v>
+      </c>
+      <c r="F2267">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2268" s="1">
+        <v>2266</v>
+      </c>
+      <c r="B2268" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>kPa/m -&gt; Pa/m</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E2268">
+        <v>1</v>
+      </c>
+      <c r="F2268">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2269" s="1">
+        <v>2267</v>
+      </c>
+      <c r="B2269" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>atmosphere -&gt; psia</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>563</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>554</v>
+      </c>
+      <c r="E2269">
+        <v>1</v>
+      </c>
+      <c r="F2269">
+        <v>14.695948775715101</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2270" s="1">
+        <v>2268</v>
+      </c>
+      <c r="B2270" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>psia -&gt; atmosphere</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>554</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>563</v>
+      </c>
+      <c r="E2270">
+        <v>14.695948775715101</v>
+      </c>
+      <c r="F2270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2271" s="1">
+        <v>2269</v>
+      </c>
+      <c r="B2271" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>m/s -&gt; ft/sec</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D2271" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E2271">
+        <v>1</v>
+      </c>
+      <c r="F2271">
+        <v>3.280839895013123</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2272" s="1">
+        <v>2270</v>
+      </c>
+      <c r="B2272" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>m/s -&gt; km/h</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E2272">
+        <v>1</v>
+      </c>
+      <c r="F2272">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2273" s="1">
+        <v>2271</v>
+      </c>
+      <c r="B2273" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>Darcy -&gt; mD</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>922</v>
+      </c>
+      <c r="D2273" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E2273">
+        <v>1</v>
+      </c>
+      <c r="F2273">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2274" s="1">
+        <v>2272</v>
+      </c>
+      <c r="B2274" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>mD -&gt; µm2</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2274">
+        <v>1</v>
+      </c>
+      <c r="F2274">
+        <v>9.869232999999999E-4</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2275" s="1">
+        <v>2273</v>
+      </c>
+      <c r="B2275" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>API -&gt; g/cc</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>831</v>
+      </c>
+      <c r="D2275" t="s">
+        <v>840</v>
+      </c>
+      <c r="E2275">
+        <v>10</v>
+      </c>
+      <c r="F2275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2276" s="1">
+        <v>2274</v>
+      </c>
+      <c r="B2276" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>API -&gt; g/cc</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>831</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>840</v>
+      </c>
+      <c r="E2276">
+        <v>60</v>
+      </c>
+      <c r="F2276">
+        <v>0.73890339425587404</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2277" s="1">
+        <v>2275</v>
+      </c>
+      <c r="B2277" s="2" t="str">
+        <f t="shared" si="37"/>
+        <v>scf/stb -&gt; sm3/sm3</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D2277" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E2277">
+        <v>1</v>
+      </c>
+      <c r="F2277">
+        <v>0.17810769813021299</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2278" s="1">
+        <v>2276</v>
+      </c>
+      <c r="B2278" s="2" t="str">
+        <f t="shared" ref="B2278:B2294" si="38">C2278&amp;" -&gt; " &amp;D2278</f>
+        <v>Celsius -&gt; Fahrenheit</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2278">
+        <v>0</v>
+      </c>
+      <c r="F2278">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2279" s="1">
+        <v>2277</v>
+      </c>
+      <c r="B2279" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>Celsius -&gt; Fahrenheit</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2279" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2279">
+        <v>100</v>
+      </c>
+      <c r="F2279">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2280" s="1">
+        <v>2278</v>
+      </c>
+      <c r="B2280" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>Celsius -&gt; Fahrenheit</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2280">
+        <v>-40</v>
+      </c>
+      <c r="F2280">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2281" s="1">
+        <v>2279</v>
+      </c>
+      <c r="B2281" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>Fahrenheit -&gt; Kelvin</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2281" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2281">
+        <v>32</v>
+      </c>
+      <c r="F2281">
+        <v>273.14999999999998</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2282" s="1">
+        <v>2280</v>
+      </c>
+      <c r="B2282" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>Fahrenheit -&gt; Kelvin</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2282">
+        <v>212</v>
+      </c>
+      <c r="F2282">
+        <v>373.15</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2283" s="1">
+        <v>2281</v>
+      </c>
+      <c r="B2283" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>Celsius -&gt; Rankine</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2283" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2283">
+        <v>0</v>
+      </c>
+      <c r="F2283">
+        <v>491.67</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2284" s="1">
+        <v>2282</v>
+      </c>
+      <c r="B2284" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>Kelvin -&gt; Fahrenheit</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2284">
+        <v>0</v>
+      </c>
+      <c r="F2284">
+        <v>-459.67</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2285" s="1">
+        <v>2283</v>
+      </c>
+      <c r="B2285" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>psi gauge -&gt; psia</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>606</v>
+      </c>
+      <c r="D2285" t="s">
+        <v>554</v>
+      </c>
+      <c r="E2285">
+        <v>0</v>
+      </c>
+      <c r="F2285">
+        <v>14.6959</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2286" s="1">
+        <v>2284</v>
+      </c>
+      <c r="B2286" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>bar gauge -&gt; bara</v>
+      </c>
+      <c r="C2286" t="s">
+        <v>611</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>559</v>
+      </c>
+      <c r="E2286">
+        <v>0</v>
+      </c>
+      <c r="F2286">
+        <v>1.01325</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2287" s="1">
+        <v>2285</v>
+      </c>
+      <c r="B2287" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>psi gauge -&gt; Pascal</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>606</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>566</v>
+      </c>
+      <c r="E2287">
+        <v>0</v>
+      </c>
+      <c r="F2287">
+        <v>101325</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2288" s="1">
+        <v>2286</v>
+      </c>
+      <c r="B2288" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>bar gauge -&gt; Pascal</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>611</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>566</v>
+      </c>
+      <c r="E2288">
+        <v>0</v>
+      </c>
+      <c r="F2288">
+        <v>101325</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2289" s="1">
+        <v>2287</v>
+      </c>
+      <c r="B2289" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>psig/ft -&gt; kPa/m</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D2289" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E2289">
+        <v>1</v>
+      </c>
+      <c r="F2289">
+        <v>22.6206</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2290" s="1">
+        <v>2288</v>
+      </c>
+      <c r="B2290" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>psia/ft -&gt; kPa/m</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>846</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E2290">
+        <v>1</v>
+      </c>
+      <c r="F2290">
+        <v>22.6206</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2291" s="1">
+        <v>2289</v>
+      </c>
+      <c r="B2291" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>psi/ft -&gt; kPa/m</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>844</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E2291">
+        <v>1</v>
+      </c>
+      <c r="F2291">
+        <v>22.6206</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2292" s="1">
+        <v>2290</v>
+      </c>
+      <c r="B2292" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>psig/ft -&gt; MPa/km</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E2292">
+        <v>1</v>
+      </c>
+      <c r="F2292">
+        <v>22.6206</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2293" s="1">
+        <v>2291</v>
+      </c>
+      <c r="B2293" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>lb/ft3 -&gt; kPa/m</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>843</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E2293">
+        <v>1</v>
+      </c>
+      <c r="F2293">
+        <v>0.157087</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2294" s="1">
+        <v>2292</v>
+      </c>
+      <c r="B2294" s="2" t="str">
+        <f t="shared" si="38"/>
+        <v>SgO -&gt; MPa/km</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>833</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E2294">
+        <v>0.8</v>
+      </c>
+      <c r="F2294">
+        <v>7.845600000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F2256" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F2265" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
